--- a/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>469200</v>
+        <v>61400</v>
       </c>
       <c r="E8" s="3">
-        <v>493600</v>
+        <v>65200</v>
       </c>
       <c r="F8" s="3">
-        <v>478900</v>
+        <v>68600</v>
       </c>
       <c r="G8" s="3">
-        <v>468500</v>
+        <v>66600</v>
       </c>
       <c r="H8" s="3">
-        <v>456000</v>
+        <v>65100</v>
       </c>
       <c r="I8" s="3">
-        <v>451500</v>
+        <v>63400</v>
       </c>
       <c r="J8" s="3">
+        <v>62800</v>
+      </c>
+      <c r="K8" s="3">
         <v>2800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>67900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>68500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>66400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>72500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>74000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>84300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>92300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>116900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>129500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>138400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>148400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>156200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>154400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>153100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>159700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>139300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>115800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>93200</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>264300</v>
+        <v>35700</v>
       </c>
       <c r="E9" s="3">
-        <v>267600</v>
+        <v>36700</v>
       </c>
       <c r="F9" s="3">
-        <v>280900</v>
+        <v>37200</v>
       </c>
       <c r="G9" s="3">
-        <v>280400</v>
+        <v>39000</v>
       </c>
       <c r="H9" s="3">
-        <v>263900</v>
+        <v>39000</v>
       </c>
       <c r="I9" s="3">
-        <v>280500</v>
+        <v>36700</v>
       </c>
       <c r="J9" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K9" s="3">
         <v>324700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>44200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>42900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>41300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>42800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>46600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>48100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>54200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>62500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>63700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>68300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>73000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>69500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>67000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>69700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>60000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>45900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>204900</v>
+        <v>25700</v>
       </c>
       <c r="E10" s="3">
-        <v>226000</v>
+        <v>28500</v>
       </c>
       <c r="F10" s="3">
-        <v>198000</v>
+        <v>31400</v>
       </c>
       <c r="G10" s="3">
-        <v>188100</v>
+        <v>27500</v>
       </c>
       <c r="H10" s="3">
-        <v>192100</v>
+        <v>26200</v>
       </c>
       <c r="I10" s="3">
-        <v>171000</v>
+        <v>26700</v>
       </c>
       <c r="J10" s="3">
+        <v>23800</v>
+      </c>
+      <c r="K10" s="3">
         <v>-321900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>32000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>29700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>31100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>37700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>44200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>62600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>67000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>74800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>80100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>83200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>85000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>86000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>90100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>79300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>69900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>413800</v>
+        <v>51900</v>
       </c>
       <c r="E17" s="3">
-        <v>426700</v>
+        <v>57500</v>
       </c>
       <c r="F17" s="3">
-        <v>448900</v>
+        <v>59300</v>
       </c>
       <c r="G17" s="3">
-        <v>405800</v>
+        <v>62400</v>
       </c>
       <c r="H17" s="3">
-        <v>434600</v>
+        <v>56400</v>
       </c>
       <c r="I17" s="3">
-        <v>393000</v>
+        <v>60400</v>
       </c>
       <c r="J17" s="3">
+        <v>54600</v>
+      </c>
+      <c r="K17" s="3">
         <v>123100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>61500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>57400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>48400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>62000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>68000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>97300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>79400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>80000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>95700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>110900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>111700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>111800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>109800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>113500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>121900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>109900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>87900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>55400</v>
+        <v>9400</v>
       </c>
       <c r="E18" s="3">
-        <v>66900</v>
+        <v>7700</v>
       </c>
       <c r="F18" s="3">
-        <v>30000</v>
+        <v>9300</v>
       </c>
       <c r="G18" s="3">
-        <v>62700</v>
+        <v>4200</v>
       </c>
       <c r="H18" s="3">
-        <v>21400</v>
+        <v>8700</v>
       </c>
       <c r="I18" s="3">
-        <v>58500</v>
+        <v>3000</v>
       </c>
       <c r="J18" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-120300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>36800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>33800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>27600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>36800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>44400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>44700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>39600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>37800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>29400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>27900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1697,8 +1731,11 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1756,32 +1793,35 @@
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3">
         <v>38700</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>45600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>39400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>28600</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1863,174 +1903,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>55400</v>
+        <v>9400</v>
       </c>
       <c r="E23" s="3">
-        <v>66900</v>
+        <v>7700</v>
       </c>
       <c r="F23" s="3">
-        <v>30000</v>
+        <v>9300</v>
       </c>
       <c r="G23" s="3">
-        <v>62700</v>
+        <v>4200</v>
       </c>
       <c r="H23" s="3">
-        <v>21400</v>
+        <v>8700</v>
       </c>
       <c r="I23" s="3">
-        <v>58500</v>
+        <v>3000</v>
       </c>
       <c r="J23" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-120300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>27600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>44400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>39600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>37800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>29400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>27900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>11600</v>
+        <v>2100</v>
       </c>
       <c r="E24" s="3">
-        <v>17600</v>
+        <v>1600</v>
       </c>
       <c r="F24" s="3">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="G24" s="3">
-        <v>16700</v>
+        <v>300</v>
       </c>
       <c r="H24" s="3">
-        <v>3300</v>
+        <v>2300</v>
       </c>
       <c r="I24" s="3">
-        <v>15400</v>
+        <v>500</v>
       </c>
       <c r="J24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-15700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>3400</v>
       </c>
       <c r="O24" s="3">
         <v>3400</v>
       </c>
       <c r="P24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>11700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>8500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>43800</v>
+        <v>7400</v>
       </c>
       <c r="E26" s="3">
-        <v>49300</v>
+        <v>6100</v>
       </c>
       <c r="F26" s="3">
-        <v>28100</v>
+        <v>6900</v>
       </c>
       <c r="G26" s="3">
-        <v>46000</v>
+        <v>3900</v>
       </c>
       <c r="H26" s="3">
-        <v>18100</v>
+        <v>6400</v>
       </c>
       <c r="I26" s="3">
-        <v>43100</v>
+        <v>2500</v>
       </c>
       <c r="J26" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-104600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>27300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>25100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>20600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>32900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>34600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>28200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>43800</v>
+        <v>7400</v>
       </c>
       <c r="E27" s="3">
-        <v>49300</v>
+        <v>6100</v>
       </c>
       <c r="F27" s="3">
-        <v>28100</v>
+        <v>6900</v>
       </c>
       <c r="G27" s="3">
-        <v>46000</v>
+        <v>3900</v>
       </c>
       <c r="H27" s="3">
-        <v>18100</v>
+        <v>6400</v>
       </c>
       <c r="I27" s="3">
-        <v>43100</v>
+        <v>2500</v>
       </c>
       <c r="J27" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-104600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>25100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>20600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>32900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>34600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>28200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>19400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2693,91 +2763,97 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>43800</v>
+        <v>7400</v>
       </c>
       <c r="E33" s="3">
-        <v>49300</v>
+        <v>6100</v>
       </c>
       <c r="F33" s="3">
-        <v>28100</v>
+        <v>6900</v>
       </c>
       <c r="G33" s="3">
-        <v>46000</v>
+        <v>3900</v>
       </c>
       <c r="H33" s="3">
-        <v>18100</v>
+        <v>6400</v>
       </c>
       <c r="I33" s="3">
-        <v>43100</v>
+        <v>2500</v>
       </c>
       <c r="J33" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-104600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>25100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>20600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>27300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>34600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>28200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>26100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>43800</v>
+        <v>7400</v>
       </c>
       <c r="E35" s="3">
-        <v>49300</v>
+        <v>6100</v>
       </c>
       <c r="F35" s="3">
-        <v>28100</v>
+        <v>6900</v>
       </c>
       <c r="G35" s="3">
-        <v>46000</v>
+        <v>3900</v>
       </c>
       <c r="H35" s="3">
-        <v>18100</v>
+        <v>6400</v>
       </c>
       <c r="I35" s="3">
-        <v>43100</v>
+        <v>2500</v>
       </c>
       <c r="J35" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-104600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>25100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>20600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>27300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>34600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>28200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>26100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,77 +3178,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1880800</v>
+        <v>250800</v>
       </c>
       <c r="E41" s="3">
-        <v>2183300</v>
+        <v>261500</v>
       </c>
       <c r="F41" s="3">
-        <v>1772200</v>
+        <v>303500</v>
       </c>
       <c r="G41" s="3">
-        <v>1373200</v>
+        <v>246400</v>
       </c>
       <c r="H41" s="3">
-        <v>1443200</v>
+        <v>190900</v>
       </c>
       <c r="I41" s="3">
-        <v>1698000</v>
+        <v>200600</v>
       </c>
       <c r="J41" s="3">
+        <v>236100</v>
+      </c>
+      <c r="K41" s="3">
         <v>2231400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>270600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>231300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>319400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>273000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>234800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>285000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>262100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>262600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>236700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>296100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>298200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>459200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>239600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>353300</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,8 +3348,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3424,8 +3520,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3507,8 +3606,11 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3590,77 +3692,80 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10724100</v>
+        <v>1569900</v>
       </c>
       <c r="E47" s="3">
-        <v>10574700</v>
+        <v>1490900</v>
       </c>
       <c r="F47" s="3">
-        <v>11201000</v>
+        <v>1470100</v>
       </c>
       <c r="G47" s="3">
-        <v>10641400</v>
+        <v>1557200</v>
       </c>
       <c r="H47" s="3">
-        <v>10082400</v>
+        <v>1479400</v>
       </c>
       <c r="I47" s="3">
-        <v>10318200</v>
+        <v>1401700</v>
       </c>
       <c r="J47" s="3">
+        <v>1434400</v>
+      </c>
+      <c r="K47" s="3">
         <v>10415800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1662800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1704000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1472900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1331000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1325400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1416600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1627500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1700800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1754300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2077200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2235500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2303200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2469600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2500700</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3673,77 +3778,80 @@
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>35000</v>
+        <v>4600</v>
       </c>
       <c r="E48" s="3">
-        <v>32100</v>
+        <v>4900</v>
       </c>
       <c r="F48" s="3">
-        <v>32100</v>
+        <v>4500</v>
       </c>
       <c r="G48" s="3">
-        <v>18400</v>
+        <v>4500</v>
       </c>
       <c r="H48" s="3">
-        <v>21800</v>
+        <v>2600</v>
       </c>
       <c r="I48" s="3">
-        <v>17200</v>
+        <v>3000</v>
       </c>
       <c r="J48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K48" s="3">
         <v>19200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3200</v>
-      </c>
-      <c r="M48" s="3">
-        <v>3400</v>
       </c>
       <c r="N48" s="3">
         <v>3400</v>
       </c>
       <c r="O48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="P48" s="3">
         <v>3900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3300</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3756,52 +3864,55 @@
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3200</v>
+        <v>400</v>
       </c>
       <c r="E49" s="3">
-        <v>3400</v>
+        <v>400</v>
       </c>
       <c r="F49" s="3">
-        <v>3500</v>
+        <v>500</v>
       </c>
       <c r="G49" s="3">
-        <v>3600</v>
+        <v>500</v>
       </c>
       <c r="H49" s="3">
-        <v>3700</v>
+        <v>500</v>
       </c>
       <c r="I49" s="3">
-        <v>3900</v>
+        <v>500</v>
       </c>
       <c r="J49" s="3">
+        <v>500</v>
+      </c>
+      <c r="K49" s="3">
         <v>4000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>600</v>
       </c>
       <c r="L49" s="3">
         <v>600</v>
       </c>
       <c r="M49" s="3">
+        <v>600</v>
+      </c>
+      <c r="N49" s="3">
         <v>700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>400</v>
-      </c>
-      <c r="O49" s="3">
-        <v>500</v>
       </c>
       <c r="P49" s="3">
         <v>500</v>
       </c>
       <c r="Q49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R49" s="3">
         <v>600</v>
@@ -3819,13 +3930,13 @@
         <v>600</v>
       </c>
       <c r="W49" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="X49" s="3">
         <v>500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
+      <c r="Y49" s="3">
+        <v>500</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>8</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,77 +4122,80 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>108800</v>
+        <v>14300</v>
       </c>
       <c r="E52" s="3">
-        <v>98000</v>
+        <v>15100</v>
       </c>
       <c r="F52" s="3">
-        <v>76900</v>
+        <v>13600</v>
       </c>
       <c r="G52" s="3">
-        <v>23800</v>
+        <v>10700</v>
       </c>
       <c r="H52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I52" s="3">
+        <v>400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>500</v>
+      </c>
+      <c r="K52" s="3">
+        <v>21100</v>
+      </c>
+      <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3">
+        <v>13400</v>
+      </c>
+      <c r="N52" s="3">
+        <v>12100</v>
+      </c>
+      <c r="O52" s="3">
+        <v>10600</v>
+      </c>
+      <c r="P52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q52" s="3">
         <v>3000</v>
       </c>
-      <c r="I52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>21100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>13400</v>
-      </c>
-      <c r="M52" s="3">
-        <v>12100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>10600</v>
-      </c>
-      <c r="O52" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P52" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>40500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>43000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>39300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>23900</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,77 +4294,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>14474700</v>
+        <v>2119200</v>
       </c>
       <c r="E54" s="3">
-        <v>14433600</v>
+        <v>2012300</v>
       </c>
       <c r="F54" s="3">
-        <v>14481900</v>
+        <v>2006600</v>
       </c>
       <c r="G54" s="3">
-        <v>13951200</v>
+        <v>2013300</v>
       </c>
       <c r="H54" s="3">
-        <v>13126400</v>
+        <v>1939500</v>
       </c>
       <c r="I54" s="3">
-        <v>13531400</v>
+        <v>1824800</v>
       </c>
       <c r="J54" s="3">
+        <v>1881100</v>
+      </c>
+      <c r="K54" s="3">
         <v>14386200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2057100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2049700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1902000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1702900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1657700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1776800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1946900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2005800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2052200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2439100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2603200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2810900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2756600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2901400</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,8 +4446,9 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4399,71 +4530,74 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>472100</v>
+        <v>70800</v>
       </c>
       <c r="E58" s="3">
-        <v>318900</v>
+        <v>65600</v>
       </c>
       <c r="F58" s="3">
-        <v>112600</v>
+        <v>44300</v>
       </c>
       <c r="G58" s="3">
-        <v>6000</v>
+        <v>15700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I58" s="3">
-        <v>18400</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K58" s="3">
         <v>45300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>41400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>47900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>51000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>70800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>105600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>143200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>85000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>134100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>214700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>340900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>496400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>612000</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
@@ -4482,77 +4616,80 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>266500</v>
+        <v>36500</v>
       </c>
       <c r="E59" s="3">
-        <v>253300</v>
+        <v>37000</v>
       </c>
       <c r="F59" s="3">
-        <v>247100</v>
+        <v>35200</v>
       </c>
       <c r="G59" s="3">
-        <v>208100</v>
+        <v>34400</v>
       </c>
       <c r="H59" s="3">
-        <v>198100</v>
+        <v>28900</v>
       </c>
       <c r="I59" s="3">
-        <v>175100</v>
+        <v>27500</v>
       </c>
       <c r="J59" s="3">
+        <v>24300</v>
+      </c>
+      <c r="K59" s="3">
         <v>194700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>31400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>51800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>45300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>32700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>124900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>126800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>124100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>106200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>92400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>88200</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4565,8 +4702,11 @@
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4648,77 +4788,80 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6806200</v>
+        <v>996300</v>
       </c>
       <c r="E61" s="3">
-        <v>7203000</v>
+        <v>946200</v>
       </c>
       <c r="F61" s="3">
-        <v>7727600</v>
+        <v>1001400</v>
       </c>
       <c r="G61" s="3">
-        <v>7594300</v>
+        <v>1074300</v>
       </c>
       <c r="H61" s="3">
-        <v>6988100</v>
+        <v>1055800</v>
       </c>
       <c r="I61" s="3">
-        <v>7431200</v>
+        <v>971500</v>
       </c>
       <c r="J61" s="3">
+        <v>1033100</v>
+      </c>
+      <c r="K61" s="3">
         <v>8041900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1150300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1091200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>961200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>786400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>738400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>804400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1007400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1024300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1014700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1334100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1429700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1613600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1710400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1789000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4731,61 +4874,64 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>71800</v>
+        <v>9600</v>
       </c>
       <c r="E62" s="3">
-        <v>73500</v>
+        <v>10000</v>
       </c>
       <c r="F62" s="3">
-        <v>73800</v>
+        <v>10200</v>
       </c>
       <c r="G62" s="3">
-        <v>68500</v>
+        <v>10300</v>
       </c>
       <c r="H62" s="3">
-        <v>70400</v>
+        <v>9500</v>
       </c>
       <c r="I62" s="3">
-        <v>108800</v>
+        <v>9800</v>
       </c>
       <c r="J62" s="3">
+        <v>15100</v>
+      </c>
+      <c r="K62" s="3">
         <v>151800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>52000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>55700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>55200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>53200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>55300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>100</v>
-      </c>
-      <c r="T62" s="3">
-        <v>200</v>
       </c>
       <c r="U62" s="3">
         <v>200</v>
@@ -4797,11 +4943,11 @@
         <v>200</v>
       </c>
       <c r="X62" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,77 +5218,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10507600</v>
+        <v>1562500</v>
       </c>
       <c r="E66" s="3">
-        <v>10509900</v>
+        <v>1460800</v>
       </c>
       <c r="F66" s="3">
-        <v>10595900</v>
+        <v>1461100</v>
       </c>
       <c r="G66" s="3">
-        <v>10070700</v>
+        <v>1473000</v>
       </c>
       <c r="H66" s="3">
-        <v>9271100</v>
+        <v>1400000</v>
       </c>
       <c r="I66" s="3">
-        <v>9673000</v>
+        <v>1288900</v>
       </c>
       <c r="J66" s="3">
+        <v>1344700</v>
+      </c>
+      <c r="K66" s="3">
         <v>10567900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1516500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1495500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1351300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1182100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1152000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1249900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1389200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1451700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1507400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1916400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2119700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2368600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2401800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2572900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,77 +5680,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3042900</v>
+        <v>429100</v>
       </c>
       <c r="E72" s="3">
-        <v>3005600</v>
+        <v>423000</v>
       </c>
       <c r="F72" s="3">
-        <v>2958700</v>
+        <v>417800</v>
       </c>
       <c r="G72" s="3">
-        <v>2931600</v>
+        <v>411300</v>
       </c>
       <c r="H72" s="3">
-        <v>2885500</v>
+        <v>407500</v>
       </c>
       <c r="I72" s="3">
-        <v>2867400</v>
+        <v>401100</v>
       </c>
       <c r="J72" s="3">
+        <v>398600</v>
+      </c>
+      <c r="K72" s="3">
         <v>2824300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>403600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>413600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>408600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>384100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>369400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>383700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>406800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>409900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>400500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>378100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>344300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>309000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>271400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>244600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,77 +6024,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3967100</v>
+        <v>556600</v>
       </c>
       <c r="E76" s="3">
-        <v>3923700</v>
+        <v>551500</v>
       </c>
       <c r="F76" s="3">
-        <v>3886000</v>
+        <v>545500</v>
       </c>
       <c r="G76" s="3">
-        <v>3880500</v>
+        <v>540200</v>
       </c>
       <c r="H76" s="3">
-        <v>3855300</v>
+        <v>539500</v>
       </c>
       <c r="I76" s="3">
-        <v>3858500</v>
+        <v>536000</v>
       </c>
       <c r="J76" s="3">
+        <v>536400</v>
+      </c>
+      <c r="K76" s="3">
         <v>3818300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>540600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>554200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>550700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>520800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>505700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>526900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>557700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>554100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>544800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>522700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>483500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>442300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>354800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>328500</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>43800</v>
+        <v>7400</v>
       </c>
       <c r="E81" s="3">
-        <v>49300</v>
+        <v>6100</v>
       </c>
       <c r="F81" s="3">
-        <v>28100</v>
+        <v>6900</v>
       </c>
       <c r="G81" s="3">
-        <v>46000</v>
+        <v>3900</v>
       </c>
       <c r="H81" s="3">
-        <v>18100</v>
+        <v>6400</v>
       </c>
       <c r="I81" s="3">
-        <v>43100</v>
+        <v>2500</v>
       </c>
       <c r="J81" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-104600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>25100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>20600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>27300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>34600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>28200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>26100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,8 +6921,11 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,8 +7759,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,8 +7931,11 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7763,6 +8015,9 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -656,391 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>61400</v>
+        <v>59800</v>
       </c>
       <c r="E8" s="3">
-        <v>65200</v>
+        <v>61000</v>
       </c>
       <c r="F8" s="3">
-        <v>68600</v>
+        <v>64800</v>
       </c>
       <c r="G8" s="3">
-        <v>66600</v>
+        <v>68200</v>
       </c>
       <c r="H8" s="3">
-        <v>65100</v>
+        <v>66200</v>
       </c>
       <c r="I8" s="3">
-        <v>63400</v>
+        <v>64700</v>
       </c>
       <c r="J8" s="3">
+        <v>63000</v>
+      </c>
+      <c r="K8" s="3">
         <v>62800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>67900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>68500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>66400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>72500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>74000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>84300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>92300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>116900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>129500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>138400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>148400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>156200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>154400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>153100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>159700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>139300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>115800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>93200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>35700</v>
+        <v>38400</v>
       </c>
       <c r="E9" s="3">
+        <v>35400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>36500</v>
+      </c>
+      <c r="G9" s="3">
+        <v>37000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>38800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>38700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>36500</v>
+      </c>
+      <c r="K9" s="3">
+        <v>39000</v>
+      </c>
+      <c r="L9" s="3">
+        <v>324700</v>
+      </c>
+      <c r="M9" s="3">
+        <v>44200</v>
+      </c>
+      <c r="N9" s="3">
+        <v>42900</v>
+      </c>
+      <c r="O9" s="3">
+        <v>36500</v>
+      </c>
+      <c r="P9" s="3">
         <v>36700</v>
       </c>
-      <c r="F9" s="3">
-        <v>37200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>39000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>39000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>36700</v>
-      </c>
-      <c r="J9" s="3">
-        <v>39000</v>
-      </c>
-      <c r="K9" s="3">
-        <v>324700</v>
-      </c>
-      <c r="L9" s="3">
-        <v>44200</v>
-      </c>
-      <c r="M9" s="3">
-        <v>42900</v>
-      </c>
-      <c r="N9" s="3">
-        <v>36500</v>
-      </c>
-      <c r="O9" s="3">
-        <v>36700</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>41300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>42800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>46600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>48100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>54200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>62500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>63700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>68300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>73000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>69500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>67000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>69700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>60000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>45900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>25700</v>
+        <v>21300</v>
       </c>
       <c r="E10" s="3">
-        <v>28500</v>
+        <v>25500</v>
       </c>
       <c r="F10" s="3">
-        <v>31400</v>
+        <v>28300</v>
       </c>
       <c r="G10" s="3">
-        <v>27500</v>
+        <v>31200</v>
       </c>
       <c r="H10" s="3">
-        <v>26200</v>
+        <v>27400</v>
       </c>
       <c r="I10" s="3">
-        <v>26700</v>
+        <v>26000</v>
       </c>
       <c r="J10" s="3">
+        <v>26500</v>
+      </c>
+      <c r="K10" s="3">
         <v>23800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-321900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>32000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>29700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>44200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>62600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>67000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>74800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>80100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>83200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>85000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>86000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>90100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>79300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>69900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1157,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1329,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>51900</v>
+        <v>57600</v>
       </c>
       <c r="E17" s="3">
-        <v>57500</v>
+        <v>51600</v>
       </c>
       <c r="F17" s="3">
-        <v>59300</v>
+        <v>57200</v>
       </c>
       <c r="G17" s="3">
-        <v>62400</v>
+        <v>59000</v>
       </c>
       <c r="H17" s="3">
-        <v>56400</v>
+        <v>62000</v>
       </c>
       <c r="I17" s="3">
-        <v>60400</v>
+        <v>56100</v>
       </c>
       <c r="J17" s="3">
+        <v>60000</v>
+      </c>
+      <c r="K17" s="3">
         <v>54600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>123100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>61500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>57400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>52000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>48400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>68000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>97300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>79400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>80000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>95700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>110900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>111700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>111800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>109800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>113500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>121900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>109900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>87900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>9400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7700</v>
       </c>
-      <c r="F18" s="3">
-        <v>9300</v>
-      </c>
       <c r="G18" s="3">
-        <v>4200</v>
+        <v>9200</v>
       </c>
       <c r="H18" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I18" s="3">
         <v>8700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-120300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>36800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>33800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>27600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>36800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>44400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>44700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>39600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>37800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>29400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>27900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,8 +1680,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1734,8 +1767,11 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1796,32 +1832,35 @@
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>38700</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>45600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3">
         <v>39400</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3">
         <v>28600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1906,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>9400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7700</v>
       </c>
-      <c r="F23" s="3">
-        <v>9300</v>
-      </c>
       <c r="G23" s="3">
-        <v>4200</v>
+        <v>9200</v>
       </c>
       <c r="H23" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I23" s="3">
         <v>8700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-120300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>33800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>27600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>36800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>44700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>39600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>37800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>29400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>27900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>500</v>
+      </c>
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-15700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>3400</v>
       </c>
       <c r="P24" s="3">
         <v>3400</v>
       </c>
       <c r="Q24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>11500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>11400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7400</v>
+        <v>2600</v>
       </c>
       <c r="E26" s="3">
-        <v>6100</v>
+        <v>7300</v>
       </c>
       <c r="F26" s="3">
-        <v>6900</v>
+        <v>6000</v>
       </c>
       <c r="G26" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H26" s="3">
         <v>3900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-104600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>25100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>20600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>32900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>34600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>28200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7400</v>
+        <v>2600</v>
       </c>
       <c r="E27" s="3">
-        <v>6100</v>
+        <v>7300</v>
       </c>
       <c r="F27" s="3">
-        <v>6900</v>
+        <v>6000</v>
       </c>
       <c r="G27" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H27" s="3">
         <v>3900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-104600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>25100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>20600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>32900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>34600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>28200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2746,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2766,94 +2835,100 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7400</v>
+        <v>2600</v>
       </c>
       <c r="E33" s="3">
-        <v>6100</v>
+        <v>7300</v>
       </c>
       <c r="F33" s="3">
-        <v>6900</v>
+        <v>6000</v>
       </c>
       <c r="G33" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H33" s="3">
         <v>3900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-104600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>25100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>20600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>27300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>32900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>34600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>28200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>26100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7400</v>
+        <v>2600</v>
       </c>
       <c r="E35" s="3">
-        <v>6100</v>
+        <v>7300</v>
       </c>
       <c r="F35" s="3">
-        <v>6900</v>
+        <v>6000</v>
       </c>
       <c r="G35" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H35" s="3">
         <v>3900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-104600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>25100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>20600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>27300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>32900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>34600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>28200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>26100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,80 +3264,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>250800</v>
+        <v>276500</v>
       </c>
       <c r="E41" s="3">
-        <v>261500</v>
+        <v>249200</v>
       </c>
       <c r="F41" s="3">
-        <v>303500</v>
+        <v>259800</v>
       </c>
       <c r="G41" s="3">
-        <v>246400</v>
+        <v>301600</v>
       </c>
       <c r="H41" s="3">
-        <v>190900</v>
+        <v>244800</v>
       </c>
       <c r="I41" s="3">
-        <v>200600</v>
+        <v>189700</v>
       </c>
       <c r="J41" s="3">
+        <v>199400</v>
+      </c>
+      <c r="K41" s="3">
         <v>236100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2231400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>270600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>231300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>319400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>273000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>234800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>285000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>262100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>262600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>236700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>296100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>298200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>459200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>239600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>353300</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3265,8 +3351,11 @@
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,8 +3440,11 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3437,8 +3529,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3523,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3609,8 +3707,11 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3695,80 +3796,83 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1569900</v>
+        <v>1669300</v>
       </c>
       <c r="E47" s="3">
-        <v>1490900</v>
+        <v>1560200</v>
       </c>
       <c r="F47" s="3">
-        <v>1470100</v>
+        <v>1481600</v>
       </c>
       <c r="G47" s="3">
-        <v>1557200</v>
+        <v>1461000</v>
       </c>
       <c r="H47" s="3">
-        <v>1479400</v>
+        <v>1547500</v>
       </c>
       <c r="I47" s="3">
-        <v>1401700</v>
+        <v>1470200</v>
       </c>
       <c r="J47" s="3">
+        <v>1393000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1434400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10415800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1662800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1704000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1472900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1331000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1325400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1416600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1627500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1700800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1754300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2077200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2235500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2303200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2469600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2500700</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3781,80 +3885,83 @@
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4600</v>
       </c>
-      <c r="E48" s="3">
-        <v>4900</v>
-      </c>
       <c r="F48" s="3">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="G48" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="H48" s="3">
-        <v>2600</v>
+        <v>4400</v>
       </c>
       <c r="I48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J48" s="3">
         <v>3000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3200</v>
-      </c>
-      <c r="N48" s="3">
-        <v>3400</v>
       </c>
       <c r="O48" s="3">
         <v>3400</v>
       </c>
       <c r="P48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Q48" s="3">
         <v>3900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3300</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3867,8 +3974,11 @@
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3879,7 +3989,7 @@
         <v>400</v>
       </c>
       <c r="F49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G49" s="3">
         <v>500</v>
@@ -3894,28 +4004,28 @@
         <v>500</v>
       </c>
       <c r="K49" s="3">
+        <v>500</v>
+      </c>
+      <c r="L49" s="3">
         <v>4000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>600</v>
       </c>
       <c r="M49" s="3">
         <v>600</v>
       </c>
       <c r="N49" s="3">
+        <v>600</v>
+      </c>
+      <c r="O49" s="3">
         <v>700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>400</v>
-      </c>
-      <c r="P49" s="3">
-        <v>500</v>
       </c>
       <c r="Q49" s="3">
         <v>500</v>
       </c>
       <c r="R49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>600</v>
@@ -3933,13 +4043,13 @@
         <v>600</v>
       </c>
       <c r="X49" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Y49" s="3">
         <v>500</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
+      <c r="Z49" s="3">
+        <v>500</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
@@ -3953,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,80 +4241,83 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>14300</v>
+        <v>12700</v>
       </c>
       <c r="E52" s="3">
-        <v>15100</v>
+        <v>14200</v>
       </c>
       <c r="F52" s="3">
-        <v>13600</v>
+        <v>15000</v>
       </c>
       <c r="G52" s="3">
-        <v>10700</v>
+        <v>13500</v>
       </c>
       <c r="H52" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I52" s="3">
         <v>3300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>40500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>39300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>31600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>26300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>23900</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4211,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,80 +4419,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2119200</v>
+        <v>2260900</v>
       </c>
       <c r="E54" s="3">
-        <v>2012300</v>
+        <v>2106100</v>
       </c>
       <c r="F54" s="3">
-        <v>2006600</v>
+        <v>1999800</v>
       </c>
       <c r="G54" s="3">
-        <v>2013300</v>
+        <v>1994100</v>
       </c>
       <c r="H54" s="3">
-        <v>1939500</v>
+        <v>2000800</v>
       </c>
       <c r="I54" s="3">
-        <v>1824800</v>
+        <v>1927500</v>
       </c>
       <c r="J54" s="3">
+        <v>1813500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1881100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14386200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2057100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2049700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1902000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1702900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1657700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1776800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1946900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2005800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2052200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2439100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2603200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2810900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2756600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2901400</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4383,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,8 +4576,9 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4533,74 +4663,77 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>94900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>70300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>65200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>44100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>15600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>800</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L58" s="3">
+        <v>45300</v>
+      </c>
+      <c r="M58" s="3">
+        <v>41400</v>
+      </c>
+      <c r="N58" s="3">
+        <v>47900</v>
+      </c>
+      <c r="O58" s="3">
+        <v>51000</v>
+      </c>
+      <c r="P58" s="3">
         <v>70800</v>
       </c>
-      <c r="E58" s="3">
-        <v>65600</v>
-      </c>
-      <c r="F58" s="3">
-        <v>44300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>15700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>800</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>45300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>41400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>47900</v>
-      </c>
-      <c r="N58" s="3">
-        <v>51000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>70800</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>105600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>143200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>85000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>134100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>214700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>340900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>496400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>612000</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
@@ -4619,80 +4752,83 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>36500</v>
+        <v>32200</v>
       </c>
       <c r="E59" s="3">
-        <v>37000</v>
+        <v>36200</v>
       </c>
       <c r="F59" s="3">
-        <v>35200</v>
+        <v>36800</v>
       </c>
       <c r="G59" s="3">
-        <v>34400</v>
+        <v>35000</v>
       </c>
       <c r="H59" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>28700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>27400</v>
+      </c>
+      <c r="K59" s="3">
+        <v>24300</v>
+      </c>
+      <c r="L59" s="3">
+        <v>194700</v>
+      </c>
+      <c r="M59" s="3">
+        <v>31400</v>
+      </c>
+      <c r="N59" s="3">
+        <v>27600</v>
+      </c>
+      <c r="O59" s="3">
         <v>28900</v>
       </c>
-      <c r="I59" s="3">
-        <v>27500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>24300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>194700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>31400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>27600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>28900</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>51800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>45300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>32700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>124900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>126800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>124100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>106200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>92400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>88200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4705,8 +4841,11 @@
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4791,80 +4930,83 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>996300</v>
+        <v>1138900</v>
       </c>
       <c r="E61" s="3">
-        <v>946200</v>
+        <v>990100</v>
       </c>
       <c r="F61" s="3">
-        <v>1001400</v>
+        <v>940300</v>
       </c>
       <c r="G61" s="3">
-        <v>1074300</v>
+        <v>995200</v>
       </c>
       <c r="H61" s="3">
-        <v>1055800</v>
+        <v>1067600</v>
       </c>
       <c r="I61" s="3">
-        <v>971500</v>
+        <v>1049200</v>
       </c>
       <c r="J61" s="3">
+        <v>965500</v>
+      </c>
+      <c r="K61" s="3">
         <v>1033100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8041900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1150300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1091200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>961200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>786400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>738400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>804400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1007400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1024300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1014700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1334100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1429700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1613600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1710400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1789000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -4877,64 +5019,67 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E62" s="3">
         <v>9600</v>
       </c>
-      <c r="E62" s="3">
-        <v>10000</v>
-      </c>
       <c r="F62" s="3">
+        <v>9900</v>
+      </c>
+      <c r="G62" s="3">
         <v>10200</v>
       </c>
-      <c r="G62" s="3">
-        <v>10300</v>
-      </c>
       <c r="H62" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I62" s="3">
         <v>9500</v>
       </c>
-      <c r="I62" s="3">
-        <v>9800</v>
-      </c>
       <c r="J62" s="3">
+        <v>9700</v>
+      </c>
+      <c r="K62" s="3">
         <v>15100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>151800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>52000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>55700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>55200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>53200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>55300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>100</v>
-      </c>
-      <c r="U62" s="3">
-        <v>200</v>
       </c>
       <c r="V62" s="3">
         <v>200</v>
@@ -4946,11 +5091,11 @@
         <v>200</v>
       </c>
       <c r="Y62" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z62" s="3">
         <v>100</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,80 +5375,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1562500</v>
+        <v>1707000</v>
       </c>
       <c r="E66" s="3">
-        <v>1460800</v>
+        <v>1552900</v>
       </c>
       <c r="F66" s="3">
-        <v>1461100</v>
+        <v>1451700</v>
       </c>
       <c r="G66" s="3">
-        <v>1473000</v>
+        <v>1452000</v>
       </c>
       <c r="H66" s="3">
-        <v>1400000</v>
+        <v>1463900</v>
       </c>
       <c r="I66" s="3">
-        <v>1288900</v>
+        <v>1391400</v>
       </c>
       <c r="J66" s="3">
+        <v>1280900</v>
+      </c>
+      <c r="K66" s="3">
         <v>1344700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10567900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1516500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1495500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1351300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1182100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1152000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1249900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1389200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1451700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1507400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1916400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2119700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2368600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2401800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2572900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5307,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,80 +5853,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>429100</v>
+        <v>428800</v>
       </c>
       <c r="E72" s="3">
-        <v>423000</v>
+        <v>426500</v>
       </c>
       <c r="F72" s="3">
-        <v>417800</v>
+        <v>420400</v>
       </c>
       <c r="G72" s="3">
-        <v>411300</v>
+        <v>415300</v>
       </c>
       <c r="H72" s="3">
-        <v>407500</v>
+        <v>408800</v>
       </c>
       <c r="I72" s="3">
-        <v>401100</v>
+        <v>405000</v>
       </c>
       <c r="J72" s="3">
+        <v>398700</v>
+      </c>
+      <c r="K72" s="3">
         <v>398600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2824300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>403600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>413600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>408600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>384100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>369400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>383700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>406800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>409900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>400500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>378100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>344300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>309000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>271400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>244600</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5769,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,80 +6209,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>556600</v>
+        <v>553900</v>
       </c>
       <c r="E76" s="3">
-        <v>551500</v>
+        <v>553200</v>
       </c>
       <c r="F76" s="3">
-        <v>545500</v>
+        <v>548100</v>
       </c>
       <c r="G76" s="3">
-        <v>540200</v>
+        <v>542100</v>
       </c>
       <c r="H76" s="3">
-        <v>539500</v>
+        <v>536900</v>
       </c>
       <c r="I76" s="3">
-        <v>536000</v>
+        <v>536100</v>
       </c>
       <c r="J76" s="3">
+        <v>532700</v>
+      </c>
+      <c r="K76" s="3">
         <v>536400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3818300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>540600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>554200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>550700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>520800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>505700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>526900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>557700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>554100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>544800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>522700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>483500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>442300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>354800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>328500</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6113,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7400</v>
+        <v>2600</v>
       </c>
       <c r="E81" s="3">
-        <v>6100</v>
+        <v>7300</v>
       </c>
       <c r="F81" s="3">
-        <v>6900</v>
+        <v>6000</v>
       </c>
       <c r="G81" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H81" s="3">
         <v>3900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-104600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>25100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>20600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>27300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>32900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>34600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>28200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>26100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,8 +7137,11 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7010,8 +7226,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7526,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7386,8 +7615,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,8 +8004,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7848,8 +8093,11 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7934,8 +8182,11 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8018,6 +8269,9 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>59800</v>
+        <v>140300</v>
       </c>
       <c r="E8" s="3">
         <v>61000</v>
       </c>
       <c r="F8" s="3">
-        <v>64800</v>
+        <v>62200</v>
       </c>
       <c r="G8" s="3">
-        <v>68200</v>
+        <v>66100</v>
       </c>
       <c r="H8" s="3">
-        <v>66200</v>
+        <v>69600</v>
       </c>
       <c r="I8" s="3">
-        <v>64700</v>
+        <v>67500</v>
       </c>
       <c r="J8" s="3">
+        <v>66000</v>
+      </c>
+      <c r="K8" s="3">
         <v>63000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>62800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>67900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>68500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>66400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>72500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>74000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>84300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>92300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>116900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>129500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>138400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>148400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>156200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>154400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>153100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>159700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>139300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>115800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>93200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>38400</v>
+        <v>79100</v>
       </c>
       <c r="E9" s="3">
-        <v>35400</v>
+        <v>39200</v>
       </c>
       <c r="F9" s="3">
+        <v>36200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>37300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>37700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>39600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>39500</v>
+      </c>
+      <c r="K9" s="3">
         <v>36500</v>
       </c>
-      <c r="G9" s="3">
-        <v>37000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>38800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>38700</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
+        <v>39000</v>
+      </c>
+      <c r="M9" s="3">
+        <v>324700</v>
+      </c>
+      <c r="N9" s="3">
+        <v>44200</v>
+      </c>
+      <c r="O9" s="3">
+        <v>42900</v>
+      </c>
+      <c r="P9" s="3">
         <v>36500</v>
       </c>
-      <c r="K9" s="3">
-        <v>39000</v>
-      </c>
-      <c r="L9" s="3">
-        <v>324700</v>
-      </c>
-      <c r="M9" s="3">
-        <v>44200</v>
-      </c>
-      <c r="N9" s="3">
-        <v>42900</v>
-      </c>
-      <c r="O9" s="3">
-        <v>36500</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>36700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>41300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>42800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>46600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>48100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>54200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>62500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>63700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>68300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>73000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>69500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>67000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>69700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>60000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>45900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>21300</v>
+        <v>61200</v>
       </c>
       <c r="E10" s="3">
-        <v>25500</v>
+        <v>21800</v>
       </c>
       <c r="F10" s="3">
-        <v>28300</v>
+        <v>26100</v>
       </c>
       <c r="G10" s="3">
-        <v>31200</v>
+        <v>28900</v>
       </c>
       <c r="H10" s="3">
-        <v>27400</v>
+        <v>31900</v>
       </c>
       <c r="I10" s="3">
-        <v>26000</v>
+        <v>27900</v>
       </c>
       <c r="J10" s="3">
         <v>26500</v>
       </c>
       <c r="K10" s="3">
+        <v>26500</v>
+      </c>
+      <c r="L10" s="3">
         <v>23800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-321900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>32000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>31200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>37700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>44200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>62600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>67000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>74800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>80100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>83200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>85000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>86000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>90100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>79300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>69900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>57600</v>
+        <v>132000</v>
       </c>
       <c r="E17" s="3">
-        <v>51600</v>
+        <v>58800</v>
       </c>
       <c r="F17" s="3">
+        <v>52700</v>
+      </c>
+      <c r="G17" s="3">
+        <v>58300</v>
+      </c>
+      <c r="H17" s="3">
+        <v>60200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>63300</v>
+      </c>
+      <c r="J17" s="3">
         <v>57200</v>
       </c>
-      <c r="G17" s="3">
-        <v>59000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="K17" s="3">
+        <v>60000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>54600</v>
+      </c>
+      <c r="M17" s="3">
+        <v>123100</v>
+      </c>
+      <c r="N17" s="3">
+        <v>61500</v>
+      </c>
+      <c r="O17" s="3">
+        <v>57400</v>
+      </c>
+      <c r="P17" s="3">
+        <v>52000</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>48400</v>
+      </c>
+      <c r="R17" s="3">
         <v>62000</v>
       </c>
-      <c r="I17" s="3">
-        <v>56100</v>
-      </c>
-      <c r="J17" s="3">
-        <v>60000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>54600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>123100</v>
-      </c>
-      <c r="M17" s="3">
-        <v>61500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>57400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>52000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>48400</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>62000</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>68000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>97300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>79400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>80000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>95700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>110900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>111700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>111800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>109800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>113500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>121900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>109900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>87900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2100</v>
+        <v>8300</v>
       </c>
       <c r="E18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H18" s="3">
         <v>9400</v>
       </c>
-      <c r="F18" s="3">
-        <v>7700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>4100</v>
-      </c>
       <c r="I18" s="3">
-        <v>8700</v>
+        <v>4200</v>
       </c>
       <c r="J18" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K18" s="3">
         <v>3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-120300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>36800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>33800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>27600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>36800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>44400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>44700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>39600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>37800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>29400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>27900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1770,8 +1804,11 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1835,32 +1872,35 @@
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>38700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>45600</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>39400</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3">
         <v>28600</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2100</v>
+        <v>8300</v>
       </c>
       <c r="E23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F23" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G23" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H23" s="3">
         <v>9400</v>
       </c>
-      <c r="F23" s="3">
-        <v>7700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>4100</v>
-      </c>
       <c r="I23" s="3">
-        <v>8700</v>
+        <v>4200</v>
       </c>
       <c r="J23" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K23" s="3">
         <v>3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-120300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>33800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>27600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>44400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>44700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>39600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>37800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>29400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>27900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
-        <v>2000</v>
-      </c>
       <c r="F24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
-        <v>300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-15700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>3400</v>
       </c>
       <c r="Q24" s="3">
         <v>3400</v>
       </c>
       <c r="R24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>12400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E26" s="3">
         <v>2600</v>
       </c>
-      <c r="E26" s="3">
-        <v>7300</v>
-      </c>
       <c r="F26" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G26" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L26" s="3">
         <v>6000</v>
       </c>
-      <c r="G26" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H26" s="3">
-        <v>3900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-104600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>25100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>20600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>27300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>32900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>34600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>28200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>17000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>19400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E27" s="3">
         <v>2600</v>
       </c>
-      <c r="E27" s="3">
-        <v>7300</v>
-      </c>
       <c r="F27" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G27" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="G27" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>3900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-104600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>25100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>20600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>27300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>32900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>34600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>28200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>26100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>19400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2838,97 +2908,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E33" s="3">
         <v>2600</v>
       </c>
-      <c r="E33" s="3">
-        <v>7300</v>
-      </c>
       <c r="F33" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G33" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="G33" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>3900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-104600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>25100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>20600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>27300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>34600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>28200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>26100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>19400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E35" s="3">
         <v>2600</v>
       </c>
-      <c r="E35" s="3">
-        <v>7300</v>
-      </c>
       <c r="F35" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G35" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="G35" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>3900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-104600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>25100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>20600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>27300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>34600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>28200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>26100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>19400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,83 +3351,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>276500</v>
+        <v>227300</v>
       </c>
       <c r="E41" s="3">
-        <v>249200</v>
+        <v>282200</v>
       </c>
       <c r="F41" s="3">
-        <v>259800</v>
+        <v>254300</v>
       </c>
       <c r="G41" s="3">
-        <v>301600</v>
+        <v>265100</v>
       </c>
       <c r="H41" s="3">
-        <v>244800</v>
+        <v>307800</v>
       </c>
       <c r="I41" s="3">
-        <v>189700</v>
+        <v>249800</v>
       </c>
       <c r="J41" s="3">
+        <v>193600</v>
+      </c>
+      <c r="K41" s="3">
         <v>199400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>236100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2231400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>270600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>231300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>319400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>273000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>234800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>285000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>262100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>262600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>236700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>296100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>298200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>459200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>239600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>353300</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3710,8 +3809,11 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3799,83 +3901,86 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1669300</v>
+        <v>1849900</v>
       </c>
       <c r="E47" s="3">
-        <v>1560200</v>
+        <v>1703400</v>
       </c>
       <c r="F47" s="3">
-        <v>1481600</v>
+        <v>1592000</v>
       </c>
       <c r="G47" s="3">
-        <v>1461000</v>
+        <v>1511900</v>
       </c>
       <c r="H47" s="3">
-        <v>1547500</v>
+        <v>1490800</v>
       </c>
       <c r="I47" s="3">
-        <v>1470200</v>
+        <v>1579100</v>
       </c>
       <c r="J47" s="3">
+        <v>1500200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1393000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1434400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10415800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1662800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1704000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1472900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1331000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1325400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1416600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1627500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1700800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1754300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2077200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2235500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2303200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2469600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2500700</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3888,83 +3993,86 @@
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="E48" s="3">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="F48" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="G48" s="3">
-        <v>4400</v>
+        <v>4900</v>
       </c>
       <c r="H48" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="I48" s="3">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="J48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K48" s="3">
         <v>3000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3200</v>
-      </c>
-      <c r="O48" s="3">
-        <v>3400</v>
       </c>
       <c r="P48" s="3">
         <v>3400</v>
       </c>
       <c r="Q48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R48" s="3">
         <v>3900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>15200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3300</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4007,28 +4118,28 @@
         <v>500</v>
       </c>
       <c r="L49" s="3">
+        <v>500</v>
+      </c>
+      <c r="M49" s="3">
         <v>4000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>600</v>
       </c>
       <c r="N49" s="3">
         <v>600</v>
       </c>
       <c r="O49" s="3">
+        <v>600</v>
+      </c>
+      <c r="P49" s="3">
         <v>700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>400</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>500</v>
       </c>
       <c r="R49" s="3">
         <v>500</v>
       </c>
       <c r="S49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T49" s="3">
         <v>600</v>
@@ -4046,13 +4157,13 @@
         <v>600</v>
       </c>
       <c r="Y49" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Z49" s="3">
         <v>500</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
+      <c r="AA49" s="3">
+        <v>500</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,83 +4361,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12700</v>
+        <v>15200</v>
       </c>
       <c r="E52" s="3">
-        <v>14200</v>
+        <v>13000</v>
       </c>
       <c r="F52" s="3">
-        <v>15000</v>
+        <v>14500</v>
       </c>
       <c r="G52" s="3">
-        <v>13500</v>
+        <v>15300</v>
       </c>
       <c r="H52" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>10800</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K52" s="3">
+        <v>400</v>
+      </c>
+      <c r="L52" s="3">
+        <v>500</v>
+      </c>
+      <c r="M52" s="3">
+        <v>21100</v>
+      </c>
+      <c r="N52" s="3">
+        <v>900</v>
+      </c>
+      <c r="O52" s="3">
+        <v>13400</v>
+      </c>
+      <c r="P52" s="3">
+        <v>12100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>10600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="R52" s="3">
         <v>3300</v>
       </c>
-      <c r="J52" s="3">
-        <v>400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>21100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>13400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>12100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>10600</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>3300</v>
-      </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>40500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>43000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>39300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>31600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>23900</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,83 +4545,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2260900</v>
+        <v>2436000</v>
       </c>
       <c r="E54" s="3">
-        <v>2106100</v>
+        <v>2307000</v>
       </c>
       <c r="F54" s="3">
-        <v>1999800</v>
+        <v>2149000</v>
       </c>
       <c r="G54" s="3">
-        <v>1994100</v>
+        <v>2040600</v>
       </c>
       <c r="H54" s="3">
-        <v>2000800</v>
+        <v>2034800</v>
       </c>
       <c r="I54" s="3">
-        <v>1927500</v>
+        <v>2041700</v>
       </c>
       <c r="J54" s="3">
+        <v>1966800</v>
+      </c>
+      <c r="K54" s="3">
         <v>1813500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1881100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14386200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2057100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2049700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1902000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1702900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1657700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1776800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1946900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2005800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2052200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2439100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2603200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2810900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2756600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2901400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4666,77 +4797,80 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>94900</v>
+        <v>170700</v>
       </c>
       <c r="E58" s="3">
-        <v>70300</v>
+        <v>96800</v>
       </c>
       <c r="F58" s="3">
-        <v>65200</v>
+        <v>71800</v>
       </c>
       <c r="G58" s="3">
-        <v>44100</v>
+        <v>66600</v>
       </c>
       <c r="H58" s="3">
-        <v>15600</v>
+        <v>45000</v>
       </c>
       <c r="I58" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>2600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>45300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>47900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>51000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>70800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>105600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>143200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>85000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>134100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>214700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>340900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>496400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>612000</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
@@ -4755,83 +4889,86 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>32200</v>
+        <v>32000</v>
       </c>
       <c r="E59" s="3">
-        <v>36200</v>
+        <v>32800</v>
       </c>
       <c r="F59" s="3">
-        <v>36800</v>
+        <v>37000</v>
       </c>
       <c r="G59" s="3">
-        <v>35000</v>
+        <v>37600</v>
       </c>
       <c r="H59" s="3">
-        <v>34100</v>
+        <v>35700</v>
       </c>
       <c r="I59" s="3">
-        <v>28700</v>
+        <v>34800</v>
       </c>
       <c r="J59" s="3">
+        <v>29300</v>
+      </c>
+      <c r="K59" s="3">
         <v>27400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>194700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>31400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>28400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>51800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>45300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>27300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>32700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>124900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>126800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>124100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>106200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>92400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>88200</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4844,8 +4981,11 @@
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4933,83 +5073,86 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1138900</v>
+        <v>1172500</v>
       </c>
       <c r="E61" s="3">
-        <v>990100</v>
+        <v>1162200</v>
       </c>
       <c r="F61" s="3">
-        <v>940300</v>
+        <v>1010300</v>
       </c>
       <c r="G61" s="3">
-        <v>995200</v>
+        <v>959500</v>
       </c>
       <c r="H61" s="3">
-        <v>1067600</v>
+        <v>1015500</v>
       </c>
       <c r="I61" s="3">
-        <v>1049200</v>
+        <v>1089400</v>
       </c>
       <c r="J61" s="3">
+        <v>1070600</v>
+      </c>
+      <c r="K61" s="3">
         <v>965500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1033100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8041900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1150300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1091200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>961200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>786400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>738400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>804400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1007400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1024300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1014700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1334100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1429700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1613600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1710400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1789000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5022,67 +5165,70 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10000</v>
+        <v>10200</v>
       </c>
       <c r="E62" s="3">
-        <v>9600</v>
+        <v>10200</v>
       </c>
       <c r="F62" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="G62" s="3">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="H62" s="3">
-        <v>10200</v>
+        <v>10400</v>
       </c>
       <c r="I62" s="3">
-        <v>9500</v>
+        <v>10400</v>
       </c>
       <c r="J62" s="3">
         <v>9700</v>
       </c>
       <c r="K62" s="3">
+        <v>9700</v>
+      </c>
+      <c r="L62" s="3">
         <v>15100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>151800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>55700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>55200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>30900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>53200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>55300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>100</v>
-      </c>
-      <c r="V62" s="3">
-        <v>200</v>
       </c>
       <c r="W62" s="3">
         <v>200</v>
@@ -5094,11 +5240,11 @@
         <v>200</v>
       </c>
       <c r="Z62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA62" s="3">
         <v>100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,83 +5533,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1707000</v>
+        <v>1863800</v>
       </c>
       <c r="E66" s="3">
-        <v>1552900</v>
+        <v>1741900</v>
       </c>
       <c r="F66" s="3">
+        <v>1584600</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1481400</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1481700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1493800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1419800</v>
+      </c>
+      <c r="K66" s="3">
+        <v>1280900</v>
+      </c>
+      <c r="L66" s="3">
+        <v>1344700</v>
+      </c>
+      <c r="M66" s="3">
+        <v>10567900</v>
+      </c>
+      <c r="N66" s="3">
+        <v>1516500</v>
+      </c>
+      <c r="O66" s="3">
+        <v>1495500</v>
+      </c>
+      <c r="P66" s="3">
+        <v>1351300</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>1182100</v>
+      </c>
+      <c r="R66" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="S66" s="3">
+        <v>1249900</v>
+      </c>
+      <c r="T66" s="3">
+        <v>1389200</v>
+      </c>
+      <c r="U66" s="3">
         <v>1451700</v>
       </c>
-      <c r="G66" s="3">
-        <v>1452000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1463900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1391400</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1280900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1344700</v>
-      </c>
-      <c r="L66" s="3">
-        <v>10567900</v>
-      </c>
-      <c r="M66" s="3">
-        <v>1516500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>1495500</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1351300</v>
-      </c>
-      <c r="P66" s="3">
-        <v>1182100</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1152000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1249900</v>
-      </c>
-      <c r="S66" s="3">
-        <v>1389200</v>
-      </c>
-      <c r="T66" s="3">
-        <v>1451700</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1507400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1916400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2119700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2368600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2401800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2572900</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,83 +6027,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>428800</v>
+        <v>444400</v>
       </c>
       <c r="E72" s="3">
-        <v>426500</v>
+        <v>437600</v>
       </c>
       <c r="F72" s="3">
-        <v>420400</v>
+        <v>435200</v>
       </c>
       <c r="G72" s="3">
-        <v>415300</v>
+        <v>429000</v>
       </c>
       <c r="H72" s="3">
-        <v>408800</v>
+        <v>423700</v>
       </c>
       <c r="I72" s="3">
-        <v>405000</v>
+        <v>417100</v>
       </c>
       <c r="J72" s="3">
+        <v>413300</v>
+      </c>
+      <c r="K72" s="3">
         <v>398700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>398600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2824300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>403600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>413600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>408600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>384100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>369400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>383700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>406800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>409900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>400500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>378100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>344300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>309000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>271400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>244600</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,83 +6395,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>553900</v>
+        <v>572200</v>
       </c>
       <c r="E76" s="3">
+        <v>565200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>564500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>559300</v>
+      </c>
+      <c r="H76" s="3">
         <v>553200</v>
       </c>
-      <c r="F76" s="3">
-        <v>548100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>542100</v>
-      </c>
-      <c r="H76" s="3">
-        <v>536900</v>
-      </c>
       <c r="I76" s="3">
-        <v>536100</v>
+        <v>547800</v>
       </c>
       <c r="J76" s="3">
+        <v>547100</v>
+      </c>
+      <c r="K76" s="3">
         <v>532700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>536400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3818300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>540600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>554200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>550700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>520800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>505700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>526900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>557700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>554100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>544800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>522700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>483500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>442300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>354800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>328500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E81" s="3">
         <v>2600</v>
       </c>
-      <c r="E81" s="3">
-        <v>7300</v>
-      </c>
       <c r="F81" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G81" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="G81" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>3900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-104600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>25100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>20600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>27300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>34600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>28200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>26100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>19400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,8 +8434,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -663,10 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -705,22 +706,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44834</v>
       </c>
       <c r="K7" s="2">
         <v>44742</v>
@@ -794,25 +795,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>140300</v>
+        <v>24300</v>
       </c>
       <c r="E8" s="3">
-        <v>61000</v>
+        <v>24500</v>
       </c>
       <c r="F8" s="3">
-        <v>62200</v>
+        <v>27500</v>
       </c>
       <c r="G8" s="3">
-        <v>66100</v>
+        <v>31900</v>
       </c>
       <c r="H8" s="3">
-        <v>69600</v>
+        <v>28700</v>
       </c>
       <c r="I8" s="3">
-        <v>67500</v>
+        <v>30400</v>
       </c>
       <c r="J8" s="3">
-        <v>66000</v>
+        <v>8500</v>
       </c>
       <c r="K8" s="3">
         <v>63000</v>
@@ -886,25 +887,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>79100</v>
+        <v>11000</v>
       </c>
       <c r="E9" s="3">
-        <v>39200</v>
+        <v>11000</v>
       </c>
       <c r="F9" s="3">
-        <v>36200</v>
+        <v>12800</v>
       </c>
       <c r="G9" s="3">
-        <v>37300</v>
+        <v>11900</v>
       </c>
       <c r="H9" s="3">
-        <v>37700</v>
+        <v>11400</v>
       </c>
       <c r="I9" s="3">
-        <v>39600</v>
+        <v>12100</v>
       </c>
       <c r="J9" s="3">
-        <v>39500</v>
+        <v>11600</v>
       </c>
       <c r="K9" s="3">
         <v>36500</v>
@@ -978,25 +979,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>61200</v>
+        <v>13400</v>
       </c>
       <c r="E10" s="3">
-        <v>21800</v>
+        <v>13400</v>
       </c>
       <c r="F10" s="3">
-        <v>26100</v>
+        <v>14700</v>
       </c>
       <c r="G10" s="3">
-        <v>28900</v>
+        <v>20000</v>
       </c>
       <c r="H10" s="3">
-        <v>31900</v>
+        <v>17300</v>
       </c>
       <c r="I10" s="3">
-        <v>27900</v>
+        <v>18300</v>
       </c>
       <c r="J10" s="3">
-        <v>26500</v>
+        <v>-3000</v>
       </c>
       <c r="K10" s="3">
         <v>26500</v>
@@ -1109,8 +1110,8 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
+      <c r="F12" s="3">
+        <v>300</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1121,8 +1122,8 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="J12" s="3">
+        <v>100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1287,26 +1288,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1380,25 +1381,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1503,25 +1504,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>132000</v>
+        <v>24300</v>
       </c>
       <c r="E17" s="3">
-        <v>58800</v>
+        <v>24400</v>
       </c>
       <c r="F17" s="3">
-        <v>52700</v>
+        <v>26200</v>
       </c>
       <c r="G17" s="3">
-        <v>58300</v>
+        <v>26400</v>
       </c>
       <c r="H17" s="3">
-        <v>60200</v>
+        <v>25000</v>
       </c>
       <c r="I17" s="3">
-        <v>63300</v>
+        <v>23800</v>
       </c>
       <c r="J17" s="3">
-        <v>57200</v>
+        <v>12300</v>
       </c>
       <c r="K17" s="3">
         <v>60000</v>
@@ -1595,25 +1596,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8300</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>9600</v>
+        <v>1300</v>
       </c>
       <c r="G18" s="3">
-        <v>7800</v>
+        <v>5500</v>
       </c>
       <c r="H18" s="3">
-        <v>9400</v>
+        <v>3700</v>
       </c>
       <c r="I18" s="3">
-        <v>4200</v>
+        <v>6600</v>
       </c>
       <c r="J18" s="3">
-        <v>8800</v>
+        <v>-3800</v>
       </c>
       <c r="K18" s="3">
         <v>3000</v>
@@ -1720,26 +1721,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+        <v>-500</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1812,26 +1813,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1904,26 +1905,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1997,25 +1998,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>8300</v>
+        <v>4100</v>
       </c>
       <c r="E23" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F23" s="3">
         <v>2200</v>
       </c>
-      <c r="F23" s="3">
-        <v>9600</v>
-      </c>
       <c r="G23" s="3">
-        <v>7800</v>
+        <v>9300</v>
       </c>
       <c r="H23" s="3">
-        <v>9400</v>
+        <v>7600</v>
       </c>
       <c r="I23" s="3">
-        <v>4200</v>
+        <v>9700</v>
       </c>
       <c r="J23" s="3">
-        <v>8800</v>
+        <v>4400</v>
       </c>
       <c r="K23" s="3">
         <v>3000</v>
@@ -2089,25 +2090,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>800</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>2500</v>
-      </c>
       <c r="I24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2400</v>
       </c>
       <c r="K24" s="3">
         <v>500</v>
@@ -2273,25 +2274,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>6800</v>
+        <v>3300</v>
       </c>
       <c r="E26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F26" s="3">
         <v>2600</v>
       </c>
-      <c r="F26" s="3">
-        <v>7500</v>
-      </c>
       <c r="G26" s="3">
-        <v>6200</v>
+        <v>7300</v>
       </c>
       <c r="H26" s="3">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="I26" s="3">
-        <v>4000</v>
+        <v>7200</v>
       </c>
       <c r="J26" s="3">
-        <v>6500</v>
+        <v>4100</v>
       </c>
       <c r="K26" s="3">
         <v>2500</v>
@@ -2365,25 +2366,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6800</v>
+        <v>3300</v>
       </c>
       <c r="E27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F27" s="3">
         <v>2600</v>
       </c>
-      <c r="F27" s="3">
-        <v>7500</v>
-      </c>
       <c r="G27" s="3">
-        <v>6200</v>
+        <v>7300</v>
       </c>
       <c r="H27" s="3">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="I27" s="3">
-        <v>4000</v>
+        <v>7200</v>
       </c>
       <c r="J27" s="3">
-        <v>6500</v>
+        <v>4100</v>
       </c>
       <c r="K27" s="3">
         <v>2500</v>
@@ -2824,26 +2825,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2917,25 +2918,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6800</v>
+        <v>3300</v>
       </c>
       <c r="E33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F33" s="3">
         <v>2600</v>
       </c>
-      <c r="F33" s="3">
-        <v>7500</v>
-      </c>
       <c r="G33" s="3">
-        <v>6200</v>
+        <v>7300</v>
       </c>
       <c r="H33" s="3">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="I33" s="3">
-        <v>4000</v>
+        <v>7200</v>
       </c>
       <c r="J33" s="3">
-        <v>6500</v>
+        <v>4100</v>
       </c>
       <c r="K33" s="3">
         <v>2500</v>
@@ -3101,25 +3102,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6800</v>
+        <v>3300</v>
       </c>
       <c r="E35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F35" s="3">
         <v>2600</v>
       </c>
-      <c r="F35" s="3">
-        <v>7500</v>
-      </c>
       <c r="G35" s="3">
-        <v>6200</v>
+        <v>7300</v>
       </c>
       <c r="H35" s="3">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="I35" s="3">
-        <v>4000</v>
+        <v>7200</v>
       </c>
       <c r="J35" s="3">
-        <v>6500</v>
+        <v>4100</v>
       </c>
       <c r="K35" s="3">
         <v>2500</v>
@@ -3201,22 +3202,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44834</v>
       </c>
       <c r="K38" s="2">
         <v>44742</v>
@@ -3358,25 +3359,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>227300</v>
+        <v>221800</v>
       </c>
       <c r="E41" s="3">
-        <v>282200</v>
+        <v>223300</v>
       </c>
       <c r="F41" s="3">
-        <v>254300</v>
+        <v>282300</v>
       </c>
       <c r="G41" s="3">
-        <v>265100</v>
+        <v>247200</v>
       </c>
       <c r="H41" s="3">
-        <v>307800</v>
+        <v>259300</v>
       </c>
       <c r="I41" s="3">
-        <v>249800</v>
+        <v>317800</v>
       </c>
       <c r="J41" s="3">
-        <v>193600</v>
+        <v>256900</v>
       </c>
       <c r="K41" s="3">
         <v>199400</v>
@@ -3542,25 +3543,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>1295300</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>1303600</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>1335000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>1121900</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>1029900</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>1134000</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1292300</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3633,26 +3634,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3726,25 +3727,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>24200</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>136300</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>21300</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>22400</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>79100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3818,25 +3819,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>1983300</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>1996100</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>2102100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>1713000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1600300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>1785400</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1895800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3910,25 +3911,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1849900</v>
+        <v>44100</v>
       </c>
       <c r="E47" s="3">
-        <v>1703400</v>
+        <v>44400</v>
       </c>
       <c r="F47" s="3">
-        <v>1592000</v>
+        <v>63800</v>
       </c>
       <c r="G47" s="3">
-        <v>1511900</v>
+        <v>81900</v>
       </c>
       <c r="H47" s="3">
-        <v>1490800</v>
+        <v>137800</v>
       </c>
       <c r="I47" s="3">
-        <v>1579100</v>
+        <v>71900</v>
       </c>
       <c r="J47" s="3">
-        <v>1500200</v>
+        <v>82300</v>
       </c>
       <c r="K47" s="3">
         <v>1393000</v>
@@ -4002,25 +4003,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>30000</v>
+        <v>29300</v>
       </c>
       <c r="E48" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F48" s="3">
         <v>5100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I48" s="3">
         <v>4700</v>
       </c>
-      <c r="G48" s="3">
-        <v>4900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>4500</v>
-      </c>
       <c r="J48" s="3">
-        <v>2600</v>
+        <v>4600</v>
       </c>
       <c r="K48" s="3">
         <v>3000</v>
@@ -4103,10 +4104,10 @@
         <v>400</v>
       </c>
       <c r="G49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I49" s="3">
         <v>500</v>
@@ -4370,25 +4371,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15200</v>
+        <v>305700</v>
       </c>
       <c r="E52" s="3">
-        <v>13000</v>
+        <v>307700</v>
       </c>
       <c r="F52" s="3">
-        <v>14500</v>
+        <v>123400</v>
       </c>
       <c r="G52" s="3">
-        <v>15300</v>
+        <v>275100</v>
       </c>
       <c r="H52" s="3">
-        <v>13800</v>
+        <v>237600</v>
       </c>
       <c r="I52" s="3">
-        <v>10800</v>
+        <v>224500</v>
       </c>
       <c r="J52" s="3">
-        <v>3400</v>
+        <v>105300</v>
       </c>
       <c r="K52" s="3">
         <v>400</v>
@@ -4554,25 +4555,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2436000</v>
+        <v>2377800</v>
       </c>
       <c r="E54" s="3">
-        <v>2307000</v>
+        <v>2393000</v>
       </c>
       <c r="F54" s="3">
-        <v>2149000</v>
+        <v>2307800</v>
       </c>
       <c r="G54" s="3">
-        <v>2040600</v>
+        <v>2089100</v>
       </c>
       <c r="H54" s="3">
-        <v>2034800</v>
+        <v>1995900</v>
       </c>
       <c r="I54" s="3">
-        <v>2041700</v>
+        <v>2101200</v>
       </c>
       <c r="J54" s="3">
-        <v>1966800</v>
+        <v>2099700</v>
       </c>
       <c r="K54" s="3">
         <v>1813500</v>
@@ -4713,26 +4714,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -4806,25 +4807,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>170700</v>
+        <v>166600</v>
       </c>
       <c r="E58" s="3">
-        <v>96800</v>
+        <v>167700</v>
       </c>
       <c r="F58" s="3">
-        <v>71800</v>
+        <v>1005200</v>
       </c>
       <c r="G58" s="3">
-        <v>66600</v>
+        <v>69800</v>
       </c>
       <c r="H58" s="3">
-        <v>45000</v>
+        <v>65100</v>
       </c>
       <c r="I58" s="3">
-        <v>15900</v>
+        <v>46400</v>
       </c>
       <c r="J58" s="3">
-        <v>800</v>
+        <v>839200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4898,25 +4899,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>32000</v>
+        <v>26000</v>
       </c>
       <c r="E59" s="3">
-        <v>32800</v>
+        <v>26200</v>
       </c>
       <c r="F59" s="3">
-        <v>37000</v>
+        <v>26000</v>
       </c>
       <c r="G59" s="3">
-        <v>37600</v>
+        <v>28800</v>
       </c>
       <c r="H59" s="3">
-        <v>35700</v>
+        <v>29700</v>
       </c>
       <c r="I59" s="3">
-        <v>34800</v>
+        <v>30500</v>
       </c>
       <c r="J59" s="3">
-        <v>29300</v>
+        <v>28500</v>
       </c>
       <c r="K59" s="3">
         <v>27400</v>
@@ -4990,25 +4991,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>194900</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>196100</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1045300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>101700</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>97600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>79100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>885600</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5082,25 +5083,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1172500</v>
+        <v>1147400</v>
       </c>
       <c r="E61" s="3">
-        <v>1162200</v>
+        <v>1154800</v>
       </c>
       <c r="F61" s="3">
-        <v>1010300</v>
+        <v>257900</v>
       </c>
       <c r="G61" s="3">
-        <v>959500</v>
+        <v>986200</v>
       </c>
       <c r="H61" s="3">
-        <v>1015500</v>
+        <v>942700</v>
       </c>
       <c r="I61" s="3">
-        <v>1089400</v>
+        <v>1052800</v>
       </c>
       <c r="J61" s="3">
-        <v>1070600</v>
+        <v>301700</v>
       </c>
       <c r="K61" s="3">
         <v>965500</v>
@@ -5174,25 +5175,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10200</v>
+        <v>467000</v>
       </c>
       <c r="E62" s="3">
-        <v>10200</v>
+        <v>470000</v>
       </c>
       <c r="F62" s="3">
-        <v>9800</v>
+        <v>423400</v>
       </c>
       <c r="G62" s="3">
-        <v>10100</v>
+        <v>422200</v>
       </c>
       <c r="H62" s="3">
-        <v>10400</v>
+        <v>383800</v>
       </c>
       <c r="I62" s="3">
-        <v>10400</v>
+        <v>372700</v>
       </c>
       <c r="J62" s="3">
-        <v>9700</v>
+        <v>325700</v>
       </c>
       <c r="K62" s="3">
         <v>9700</v>
@@ -5542,25 +5543,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1863800</v>
+        <v>1819200</v>
       </c>
       <c r="E66" s="3">
-        <v>1741900</v>
+        <v>1830900</v>
       </c>
       <c r="F66" s="3">
-        <v>1584600</v>
+        <v>1742400</v>
       </c>
       <c r="G66" s="3">
-        <v>1481400</v>
+        <v>1519600</v>
       </c>
       <c r="H66" s="3">
-        <v>1481700</v>
+        <v>1434000</v>
       </c>
       <c r="I66" s="3">
-        <v>1493800</v>
+        <v>1515300</v>
       </c>
       <c r="J66" s="3">
-        <v>1419800</v>
+        <v>1528800</v>
       </c>
       <c r="K66" s="3">
         <v>1280900</v>
@@ -6036,25 +6037,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>444400</v>
+        <v>433700</v>
       </c>
       <c r="E72" s="3">
-        <v>437600</v>
+        <v>436500</v>
       </c>
       <c r="F72" s="3">
-        <v>435200</v>
+        <v>437700</v>
       </c>
       <c r="G72" s="3">
+        <v>423100</v>
+      </c>
+      <c r="H72" s="3">
+        <v>419600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>437500</v>
+      </c>
+      <c r="J72" s="3">
         <v>429000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>423700</v>
-      </c>
-      <c r="I72" s="3">
-        <v>417100</v>
-      </c>
-      <c r="J72" s="3">
-        <v>413300</v>
       </c>
       <c r="K72" s="3">
         <v>398700</v>
@@ -6404,25 +6405,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>572200</v>
+        <v>558500</v>
       </c>
       <c r="E76" s="3">
-        <v>565200</v>
+        <v>562100</v>
       </c>
       <c r="F76" s="3">
-        <v>564500</v>
+        <v>565400</v>
       </c>
       <c r="G76" s="3">
-        <v>559300</v>
+        <v>548700</v>
       </c>
       <c r="H76" s="3">
-        <v>553200</v>
+        <v>547000</v>
       </c>
       <c r="I76" s="3">
-        <v>547800</v>
+        <v>571200</v>
       </c>
       <c r="J76" s="3">
-        <v>547100</v>
+        <v>563400</v>
       </c>
       <c r="K76" s="3">
         <v>532700</v>
@@ -6596,22 +6597,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44834</v>
       </c>
       <c r="K80" s="2">
         <v>44742</v>
@@ -6685,25 +6686,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6800</v>
+        <v>3300</v>
       </c>
       <c r="E81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F81" s="3">
         <v>2600</v>
       </c>
-      <c r="F81" s="3">
-        <v>7500</v>
-      </c>
       <c r="G81" s="3">
-        <v>6200</v>
+        <v>7300</v>
       </c>
       <c r="H81" s="3">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="I81" s="3">
-        <v>4000</v>
+        <v>7200</v>
       </c>
       <c r="J81" s="3">
-        <v>6500</v>
+        <v>4100</v>
       </c>
       <c r="K81" s="3">
         <v>2500</v>
@@ -6810,26 +6811,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7362,26 +7363,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -7488,26 +7489,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7764,26 +7765,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7890,26 +7891,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8258,26 +8259,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8350,26 +8351,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8442,26 +8443,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -656,417 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F8" s="3">
         <v>24300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>24500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>27500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>31900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>28700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>30400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>63000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>62800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>65000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>67900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>68500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>66400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>72500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>74000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>84300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>92300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>116900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>129500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>138400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>148400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>156200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>154400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>153100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>159700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>139300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>115800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>93200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F9" s="3">
         <v>11000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>11000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>11900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>11400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>12100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>11600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>36500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>39000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>324700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>44200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>42900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>36500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>36700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>41300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>42800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>46600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>48100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>54200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>62500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>63700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>68300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>73000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>69500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>67000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>69700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>60000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>45900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F10" s="3">
         <v>13400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>13400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>14700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>20000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>17300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>18300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-3000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>26500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>23800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-321900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>20800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>25000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>32000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>29700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>31100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>31200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>37700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>44200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>62600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>67000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>74800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>80100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>83200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>85000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>86000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>90100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>79300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>69900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,38 +1124,40 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1191,8 +1218,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,38 +1316,44 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1375,13 +1414,19 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1402,10 +1447,10 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1467,8 +1512,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1549,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F17" s="3">
         <v>24300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>24400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>26200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>26400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>25000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>23800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>12300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>60000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>54600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>123100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>61500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>57400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>52000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>48400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>62000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>68000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>97300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>79400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>80000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>95700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>110900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>111700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>111800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>109800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>113500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>121900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>109900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>87900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>5500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>6600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>8100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-120300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>10500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>16500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>18000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>10400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>6000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-13000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>13000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>36800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>33800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>27600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>36800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>44400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>44700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>39600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>37800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>29400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>27900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,38 +1781,40 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1808,38 +1875,44 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>6700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1876,32 +1949,38 @@
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>38700</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>45600</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3">
         <v>39400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="3">
         <v>28600</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1926,11 +2005,11 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1992,192 +2071,210 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F23" s="3">
         <v>4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>9300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>7600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>9700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>8100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-120300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>10500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>16500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>18000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>10400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>6000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-13000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>12900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>36800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>33800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>27600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>36800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>44400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>44700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>39600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>37800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>29400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>27900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>2600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-15700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>3600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>9500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>8700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>6900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>9400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>11500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>10100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>11400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>11700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>12400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>8500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2365,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F26" s="3">
         <v>3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>7200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-104600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>9300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>12300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>14700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>7000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-10400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>9400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>27300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>25100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>20600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>27300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>32900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>34600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>28200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>26100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>17000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>19400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F27" s="3">
         <v>3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>7200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-104600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>9300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>12300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>14700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-10400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>9400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>27300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>25100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>20600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>27300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>32900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>34600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>28200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>26100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>17000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>19400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2659,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2636,8 +2757,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2855,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,38 +2953,44 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>400</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2912,100 +3051,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F33" s="3">
         <v>3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>7200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-104600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>9300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>12300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>14700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>7000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-10400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>9400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>27300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>25100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>20600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>27300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>32900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>34600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>28200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>26100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>17000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>19400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3247,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F35" s="3">
         <v>3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>7200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-104600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>9300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>12300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>14700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>7000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-10400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>9400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>27300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>25100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>20600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>27300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>32900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>34600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>28200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>26100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>17000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>19400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3488,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,89 +3524,91 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>160300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>166900</v>
+      </c>
+      <c r="F41" s="3">
         <v>221800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>223300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>282300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>247200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>259300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>317800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>256900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>199400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>236100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2231400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>270600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>231300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>319400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>273000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>234800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>285000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>262100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>262600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>236700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>296100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>298200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>459200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>239600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>353300</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3445,8 +3618,14 @@
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,38 +3716,44 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1016900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1058200</v>
+      </c>
+      <c r="F43" s="3">
         <v>1295300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1303600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1335000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1121900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1029900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1134000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1292300</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -3629,8 +3814,14 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3655,11 +3846,11 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3721,38 +3912,44 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>156800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>163200</v>
+      </c>
+      <c r="F45" s="3">
         <v>24000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>24200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>136300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>22000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>21300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>22400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>79100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -3813,38 +4010,44 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1817600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1891400</v>
+      </c>
+      <c r="F46" s="3">
         <v>1983300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1996100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2102100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1713000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1600300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1785400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1895800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3905,89 +4108,95 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>39900</v>
+      </c>
+      <c r="F47" s="3">
         <v>44100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>44400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>63800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>81900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>137800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>71900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>82300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1393000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1434400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>10415800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1662800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1704000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1472900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1331000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1325400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1416600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1627500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1700800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1754300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>2077200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>2235500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>2303200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>2469600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>2500700</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3997,89 +4206,95 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>30300</v>
+      </c>
+      <c r="F48" s="3">
         <v>29300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>29500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>19200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>7300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>8300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>10800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>15200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>3200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>3300</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4089,8 +4304,14 @@
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4110,10 +4331,10 @@
         <v>400</v>
       </c>
       <c r="I49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K49" s="3">
         <v>500</v>
@@ -4122,31 +4343,31 @@
         <v>500</v>
       </c>
       <c r="M49" s="3">
+        <v>500</v>
+      </c>
+      <c r="N49" s="3">
+        <v>500</v>
+      </c>
+      <c r="O49" s="3">
         <v>4000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>500</v>
-      </c>
-      <c r="T49" s="3">
-        <v>600</v>
-      </c>
-      <c r="U49" s="3">
-        <v>600</v>
       </c>
       <c r="V49" s="3">
         <v>600</v>
@@ -4161,17 +4382,17 @@
         <v>600</v>
       </c>
       <c r="Z49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB49" s="3">
         <v>500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>500</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4181,8 +4402,14 @@
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4500,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,89 +4598,95 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>155300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>161600</v>
+      </c>
+      <c r="F52" s="3">
         <v>305700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>307700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>123400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>275100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>237600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>224500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>105300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>21100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>13400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>12100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>10600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>3000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>40500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>43000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>39300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>31600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>26300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>23900</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4457,8 +4696,14 @@
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,89 +4794,95 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2058800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2142300</v>
+      </c>
+      <c r="F54" s="3">
         <v>2377800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2393000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2307800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2089100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1995900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2101200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2099700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1813500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1881100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>14386200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2057100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2049700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1902000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1702900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1657700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1776800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1946900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2005800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2052200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2439100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2603200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2810900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2756600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2901400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4641,8 +4892,14 @@
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4932,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,8 +4968,10 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4735,11 +4996,11 @@
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -4801,83 +5062,89 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>962300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1001400</v>
+      </c>
+      <c r="F58" s="3">
         <v>166600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>167700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1005200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>69800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>65100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>46400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>839200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>2600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>45300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>41400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>47900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>51000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>70800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>105600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>143200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>85000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>134100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>214700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>340900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>496400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>612000</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
@@ -4893,89 +5160,95 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>26000</v>
+        <v>28700</v>
       </c>
       <c r="E59" s="3">
-        <v>26200</v>
+        <v>29800</v>
       </c>
       <c r="F59" s="3">
         <v>26000</v>
       </c>
       <c r="G59" s="3">
+        <v>26200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>26000</v>
+      </c>
+      <c r="I59" s="3">
         <v>28800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>29700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>30500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>28500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>27400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>24300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>194700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>31400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>27600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>28900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>28400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>51800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>45300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>27300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>32700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>124900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>126800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>124100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>106200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>92400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>88200</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4985,38 +5258,44 @@
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1001600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1042200</v>
+      </c>
+      <c r="F60" s="3">
         <v>194900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>196100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1045300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>101700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>97600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>79100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>885600</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5077,89 +5356,95 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>85500</v>
+      </c>
+      <c r="F61" s="3">
         <v>1147400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1154800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>257900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>986200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>942700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1052800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>301700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>965500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1033100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8041900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1150300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1091200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>961200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>786400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>738400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>804400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1007400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1024300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1014700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1334100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1429700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1613600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1710400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1789000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5169,73 +5454,79 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>404900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>421300</v>
+      </c>
+      <c r="F62" s="3">
         <v>467000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>470000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>423400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>422200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>383800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>372700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>325700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>9700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>15100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>151800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>29100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>52000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>55700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>55200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>23200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>30900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>53200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>55300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>100</v>
-      </c>
-      <c r="W62" s="3">
-        <v>200</v>
-      </c>
-      <c r="X62" s="3">
-        <v>200</v>
       </c>
       <c r="Y62" s="3">
         <v>200</v>
@@ -5244,14 +5535,14 @@
         <v>200</v>
       </c>
       <c r="AA62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC62" s="3">
         <v>100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5261,8 +5552,14 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5650,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5748,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,89 +5846,95 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1502900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1563800</v>
+      </c>
+      <c r="F66" s="3">
         <v>1819200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1830900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1742400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1519600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1434000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1515300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1528800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1280900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1344700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>10567900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1516500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1495500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1351300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1182100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1152000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1249900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1389200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1451700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1507400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1916400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2119700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2368600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2401800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2572900</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5629,8 +5944,14 @@
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5984,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +6078,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6176,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6274,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,89 +6372,95 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>430400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>447900</v>
+      </c>
+      <c r="F72" s="3">
         <v>433700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>436500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>437700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>423100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>419600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>437500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>429000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>398700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>398600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2824300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>403600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>413600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>408600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>384100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>369400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>383700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>406800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>409900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>400500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>378100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>344300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>309000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>271400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>244600</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6123,8 +6470,14 @@
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6568,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6666,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,89 +6764,95 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>555900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>578500</v>
+      </c>
+      <c r="F76" s="3">
         <v>558500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>562100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>565400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>548700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>547000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>571200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>563400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>532700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>536400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3818300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>540600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>554200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>550700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>520800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>505700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>526900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>557700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>554100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>544800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>522700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>483500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>442300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>354800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>328500</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6491,8 +6862,14 @@
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6960,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F81" s="3">
         <v>3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>7200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-104600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>9300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>12300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>14700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>7000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-10400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>9400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>27300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>25100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>20600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>27300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>32900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>34600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>28200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>26100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>17000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>19400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,8 +7201,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6832,11 +7229,11 @@
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6898,8 +7295,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7393,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7491,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7589,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7687,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,8 +7785,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7384,11 +7817,11 @@
       <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -7450,8 +7883,14 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,8 +7923,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7510,11 +7951,11 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7576,8 +8017,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +8115,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,8 +8213,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7786,11 +8245,11 @@
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -7852,8 +8311,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8351,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7912,11 +8379,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7978,8 +8445,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8543,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8641,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,8 +8739,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8280,11 +8771,11 @@
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -8346,8 +8837,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8372,11 +8869,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8438,8 +8935,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8464,11 +8967,11 @@
       <c r="J102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -8528,6 +9031,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -807,11 +807,11 @@
       <c r="E8" s="3">
         <v>19400</v>
       </c>
-      <c r="F8" s="3">
-        <v>24300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>24500</v>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H8" s="3">
         <v>27500</v>
@@ -819,8 +819,8 @@
       <c r="I8" s="3">
         <v>31900</v>
       </c>
-      <c r="J8" s="3">
-        <v>28700</v>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K8" s="3">
         <v>30400</v>
@@ -905,11 +905,11 @@
       <c r="E9" s="3">
         <v>6700</v>
       </c>
-      <c r="F9" s="3">
-        <v>11000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>11000</v>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H9" s="3">
         <v>12800</v>
@@ -917,8 +917,8 @@
       <c r="I9" s="3">
         <v>11900</v>
       </c>
-      <c r="J9" s="3">
-        <v>11400</v>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K9" s="3">
         <v>12100</v>
@@ -1003,11 +1003,11 @@
       <c r="E10" s="3">
         <v>12700</v>
       </c>
-      <c r="F10" s="3">
-        <v>13400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>13400</v>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H10" s="3">
         <v>14700</v>
@@ -1015,8 +1015,8 @@
       <c r="I10" s="3">
         <v>20000</v>
       </c>
-      <c r="J10" s="3">
-        <v>17300</v>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K10" s="3">
         <v>18300</v>
@@ -1432,10 +1432,10 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1444,7 +1444,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1562,11 +1562,11 @@
       <c r="E17" s="3">
         <v>22000</v>
       </c>
-      <c r="F17" s="3">
-        <v>24300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>24400</v>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H17" s="3">
         <v>26200</v>
@@ -1574,8 +1574,8 @@
       <c r="I17" s="3">
         <v>26400</v>
       </c>
-      <c r="J17" s="3">
-        <v>25000</v>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K17" s="3">
         <v>23800</v>
@@ -1660,11 +1660,11 @@
       <c r="E18" s="3">
         <v>-2600</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H18" s="3">
         <v>1300</v>
@@ -1672,8 +1672,8 @@
       <c r="I18" s="3">
         <v>5500</v>
       </c>
-      <c r="J18" s="3">
-        <v>3700</v>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K18" s="3">
         <v>6600</v>
@@ -1893,10 +1893,10 @@
         <v>-2100</v>
       </c>
       <c r="F21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>1900</v>
@@ -1905,7 +1905,7 @@
         <v>5600</v>
       </c>
       <c r="J21" s="3">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>6700</v>
@@ -2088,11 +2088,11 @@
       <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>4100</v>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H23" s="3">
         <v>2200</v>
@@ -2100,8 +2100,8 @@
       <c r="I23" s="3">
         <v>9300</v>
       </c>
-      <c r="J23" s="3">
-        <v>7600</v>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K23" s="3">
         <v>9700</v>
@@ -2186,11 +2186,11 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>800</v>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3">
         <v>-400</v>
@@ -2198,8 +2198,8 @@
       <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="J24" s="3">
-        <v>1600</v>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>2600</v>
@@ -2382,11 +2382,11 @@
       <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>3300</v>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H26" s="3">
         <v>2600</v>
@@ -2394,8 +2394,8 @@
       <c r="I26" s="3">
         <v>7300</v>
       </c>
-      <c r="J26" s="3">
-        <v>6000</v>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K26" s="3">
         <v>7200</v>
@@ -2480,11 +2480,11 @@
       <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>3300</v>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H27" s="3">
         <v>2600</v>
@@ -2492,8 +2492,8 @@
       <c r="I27" s="3">
         <v>7300</v>
       </c>
-      <c r="J27" s="3">
-        <v>6000</v>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K27" s="3">
         <v>7200</v>
@@ -3068,11 +3068,11 @@
       <c r="E33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>3300</v>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H33" s="3">
         <v>2600</v>
@@ -3080,8 +3080,8 @@
       <c r="I33" s="3">
         <v>7300</v>
       </c>
-      <c r="J33" s="3">
-        <v>6000</v>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K33" s="3">
         <v>7200</v>
@@ -3264,11 +3264,11 @@
       <c r="E35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>3300</v>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H35" s="3">
         <v>2600</v>
@@ -3276,8 +3276,8 @@
       <c r="I35" s="3">
         <v>7300</v>
       </c>
-      <c r="J35" s="3">
-        <v>6000</v>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K35" s="3">
         <v>7200</v>
@@ -3537,11 +3537,11 @@
       <c r="E41" s="3">
         <v>166900</v>
       </c>
-      <c r="F41" s="3">
-        <v>221800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>223300</v>
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H41" s="3">
         <v>282300</v>
@@ -3549,8 +3549,8 @@
       <c r="I41" s="3">
         <v>247200</v>
       </c>
-      <c r="J41" s="3">
-        <v>259300</v>
+      <c r="J41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K41" s="3">
         <v>317800</v>
@@ -3733,11 +3733,11 @@
       <c r="E43" s="3">
         <v>1058200</v>
       </c>
-      <c r="F43" s="3">
-        <v>1295300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1303600</v>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H43" s="3">
         <v>1335000</v>
@@ -3745,8 +3745,8 @@
       <c r="I43" s="3">
         <v>1121900</v>
       </c>
-      <c r="J43" s="3">
-        <v>1029900</v>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K43" s="3">
         <v>1134000</v>
@@ -3929,11 +3929,11 @@
       <c r="E45" s="3">
         <v>163200</v>
       </c>
-      <c r="F45" s="3">
-        <v>24000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>24200</v>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3">
         <v>136300</v>
@@ -3941,8 +3941,8 @@
       <c r="I45" s="3">
         <v>22000</v>
       </c>
-      <c r="J45" s="3">
-        <v>21300</v>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>22400</v>
@@ -4027,11 +4027,11 @@
       <c r="E46" s="3">
         <v>1891400</v>
       </c>
-      <c r="F46" s="3">
-        <v>1983300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1996100</v>
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H46" s="3">
         <v>2102100</v>
@@ -4039,8 +4039,8 @@
       <c r="I46" s="3">
         <v>1713000</v>
       </c>
-      <c r="J46" s="3">
-        <v>1600300</v>
+      <c r="J46" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K46" s="3">
         <v>1785400</v>
@@ -4125,11 +4125,11 @@
       <c r="E47" s="3">
         <v>39900</v>
       </c>
-      <c r="F47" s="3">
-        <v>44100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>44400</v>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
         <v>63800</v>
@@ -4137,8 +4137,8 @@
       <c r="I47" s="3">
         <v>81900</v>
       </c>
-      <c r="J47" s="3">
-        <v>137800</v>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>71900</v>
@@ -4223,11 +4223,11 @@
       <c r="E48" s="3">
         <v>30300</v>
       </c>
-      <c r="F48" s="3">
-        <v>29300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>29500</v>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H48" s="3">
         <v>5100</v>
@@ -4235,8 +4235,8 @@
       <c r="I48" s="3">
         <v>4600</v>
       </c>
-      <c r="J48" s="3">
-        <v>4800</v>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K48" s="3">
         <v>4700</v>
@@ -4321,11 +4321,11 @@
       <c r="E49" s="3">
         <v>400</v>
       </c>
-      <c r="F49" s="3">
-        <v>400</v>
-      </c>
-      <c r="G49" s="3">
-        <v>400</v>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H49" s="3">
         <v>400</v>
@@ -4333,8 +4333,8 @@
       <c r="I49" s="3">
         <v>400</v>
       </c>
-      <c r="J49" s="3">
-        <v>400</v>
+      <c r="J49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K49" s="3">
         <v>500</v>
@@ -4615,11 +4615,11 @@
       <c r="E52" s="3">
         <v>161600</v>
       </c>
-      <c r="F52" s="3">
-        <v>305700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>307700</v>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3">
         <v>123400</v>
@@ -4627,8 +4627,8 @@
       <c r="I52" s="3">
         <v>275100</v>
       </c>
-      <c r="J52" s="3">
-        <v>237600</v>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>224500</v>
@@ -4811,11 +4811,11 @@
       <c r="E54" s="3">
         <v>2142300</v>
       </c>
-      <c r="F54" s="3">
-        <v>2377800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>2393000</v>
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H54" s="3">
         <v>2307800</v>
@@ -4823,8 +4823,8 @@
       <c r="I54" s="3">
         <v>2089100</v>
       </c>
-      <c r="J54" s="3">
-        <v>1995900</v>
+      <c r="J54" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K54" s="3">
         <v>2101200</v>
@@ -5079,11 +5079,11 @@
       <c r="E58" s="3">
         <v>1001400</v>
       </c>
-      <c r="F58" s="3">
-        <v>166600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>167700</v>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H58" s="3">
         <v>1005200</v>
@@ -5091,8 +5091,8 @@
       <c r="I58" s="3">
         <v>69800</v>
       </c>
-      <c r="J58" s="3">
-        <v>65100</v>
+      <c r="J58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K58" s="3">
         <v>46400</v>
@@ -5177,11 +5177,11 @@
       <c r="E59" s="3">
         <v>29800</v>
       </c>
-      <c r="F59" s="3">
-        <v>26000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>26200</v>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H59" s="3">
         <v>26000</v>
@@ -5189,8 +5189,8 @@
       <c r="I59" s="3">
         <v>28800</v>
       </c>
-      <c r="J59" s="3">
-        <v>29700</v>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K59" s="3">
         <v>30500</v>
@@ -5275,11 +5275,11 @@
       <c r="E60" s="3">
         <v>1042200</v>
       </c>
-      <c r="F60" s="3">
-        <v>194900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>196100</v>
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H60" s="3">
         <v>1045300</v>
@@ -5287,8 +5287,8 @@
       <c r="I60" s="3">
         <v>101700</v>
       </c>
-      <c r="J60" s="3">
-        <v>97600</v>
+      <c r="J60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K60" s="3">
         <v>79100</v>
@@ -5374,10 +5374,10 @@
         <v>85500</v>
       </c>
       <c r="F61" s="3">
-        <v>1147400</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>1154800</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>257900</v>
@@ -5386,7 +5386,7 @@
         <v>986200</v>
       </c>
       <c r="J61" s="3">
-        <v>942700</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>1052800</v>
@@ -5471,11 +5471,11 @@
       <c r="E62" s="3">
         <v>421300</v>
       </c>
-      <c r="F62" s="3">
-        <v>467000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>470000</v>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3">
         <v>423400</v>
@@ -5483,8 +5483,8 @@
       <c r="I62" s="3">
         <v>422200</v>
       </c>
-      <c r="J62" s="3">
-        <v>383800</v>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>372700</v>
@@ -5863,11 +5863,11 @@
       <c r="E66" s="3">
         <v>1563800</v>
       </c>
-      <c r="F66" s="3">
-        <v>1819200</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1830900</v>
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H66" s="3">
         <v>1742400</v>
@@ -5875,8 +5875,8 @@
       <c r="I66" s="3">
         <v>1519600</v>
       </c>
-      <c r="J66" s="3">
-        <v>1434000</v>
+      <c r="J66" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K66" s="3">
         <v>1515300</v>
@@ -6389,11 +6389,11 @@
       <c r="E72" s="3">
         <v>447900</v>
       </c>
-      <c r="F72" s="3">
-        <v>433700</v>
-      </c>
-      <c r="G72" s="3">
-        <v>436500</v>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H72" s="3">
         <v>437700</v>
@@ -6401,8 +6401,8 @@
       <c r="I72" s="3">
         <v>423100</v>
       </c>
-      <c r="J72" s="3">
-        <v>419600</v>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K72" s="3">
         <v>437500</v>
@@ -6781,11 +6781,11 @@
       <c r="E76" s="3">
         <v>578500</v>
       </c>
-      <c r="F76" s="3">
-        <v>558500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>562100</v>
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H76" s="3">
         <v>565400</v>
@@ -6793,8 +6793,8 @@
       <c r="I76" s="3">
         <v>548700</v>
       </c>
-      <c r="J76" s="3">
-        <v>547000</v>
+      <c r="J76" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K76" s="3">
         <v>571200</v>
@@ -7080,11 +7080,11 @@
       <c r="E81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>3300</v>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H81" s="3">
         <v>2600</v>
@@ -7092,8 +7092,8 @@
       <c r="I81" s="3">
         <v>7300</v>
       </c>
-      <c r="J81" s="3">
-        <v>6000</v>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K81" s="3">
         <v>7200</v>

--- a/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>CNF</t>
   </si>
@@ -656,440 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3">
         <v>18600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>19400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>27500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>31900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>30400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>8500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>32400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>30400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>8500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>63000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>62800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>65000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>67900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>68500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>66400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>72500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>74000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>84300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>92300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>116900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>129500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>138400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>148400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>156200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>154400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>153100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>159700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>139300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>115800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>93200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
         <v>6400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>6700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>11900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>12100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>11600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>11900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>12100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>11600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>36500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>39000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>324700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>44200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>42900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>36500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>36700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>41300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>42800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>46600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>48100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>54200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>62500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>63700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>68300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>73000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>69500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>67000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>69700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>60000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>45900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="F10" s="3">
         <v>12200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>12700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>14700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>20000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>18300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-3000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>20400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>18300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-3000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>26500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>23800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-321900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>20800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>25000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>32000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>29700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>31100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>31200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>37700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>44200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>62600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>67000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>74800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>80100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>83200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>85000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>86000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>90100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>79300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>69900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1124,44 +1148,46 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1222,8 +1248,14 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,44 +1352,50 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1418,19 +1456,25 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>400</v>
       </c>
-      <c r="E15" s="3">
-        <v>100</v>
-      </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1451,10 +1495,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1516,8 +1560,14 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,204 +1599,218 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F17" s="3">
         <v>21100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>22000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>26200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>26400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>23800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>12300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>23600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>23800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>12300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>60000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>54600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>123100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>61500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>57400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>52000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>48400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>62000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>68000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>97300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>79400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>80000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>95700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>110900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>111700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>111800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>109800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>113500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>121900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>109900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>87900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>68300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>5500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>6600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>8800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>3000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>8100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-120300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>10500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>16500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>18000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>10400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>6000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-13000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>13000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>36800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>33800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>27600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>36800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>44400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>44700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>39600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>37800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>29400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>27900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,8 +1845,10 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1793,32 +1859,32 @@
         <v>-400</v>
       </c>
       <c r="F20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1879,44 +1945,50 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>6700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>8900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1953,32 +2025,38 @@
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="3">
         <v>38700</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3">
         <v>45600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="3">
         <v>39400</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="3">
         <v>28600</v>
       </c>
-      <c r="AH21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2009,11 +2087,11 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -2075,204 +2153,222 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>9300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>9700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>8800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>9700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>8100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-120300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>10500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>16500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>18000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>10400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>6000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-13000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>12900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>36800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>33800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>27600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>36800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>44400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>44700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>39600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>37800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>29400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>27900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>24900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-7300</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-7200</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>2600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-15700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>3400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>2300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>3600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>9500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>8700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>6900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>9400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>11500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>10100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>11400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>11700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>12400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>8500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,204 +2465,222 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>7300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>7200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>6500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>7200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>6000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-104600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>9300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>12300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>14700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>7000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>3700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-10400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>9400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>27300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>25100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>20600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>27300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>32900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>34600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>28200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>26100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>17000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>19400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>7200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>6500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>7200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>6000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-104600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>9300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>12300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>14700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-10400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>9400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>27300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>25100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>20600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>27300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>32900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>34600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>28200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>26100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>17000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>19400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2777,14 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2761,8 +2881,14 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2985,14 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,8 +3089,14 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2969,32 +3107,32 @@
         <v>400</v>
       </c>
       <c r="F32" s="3">
+        <v>400</v>
+      </c>
+      <c r="G32" s="3">
+        <v>400</v>
+      </c>
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3055,106 +3193,118 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>7200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>6500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>7200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-104600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>9300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>12300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>14700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>7000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-10400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>9400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>27300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>25100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>20600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>27300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>32900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>34600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>28200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>26100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>17000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>19400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,209 +3401,227 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>7200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>6500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>7200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-104600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>9300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>12300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>14700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>7000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-10400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>9400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>27300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>25100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>20600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>27300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>32900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>34600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>28200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>26100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>17000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>19400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3656,10 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,95 +3694,97 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>47500</v>
+      </c>
+      <c r="F41" s="3">
         <v>160300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>166900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>282300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>247200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>317800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>256900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>193000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>317800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>256900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>199400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>236100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2231400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>270600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>231300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>319400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>273000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>234800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>285000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>262100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>262600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>236700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>296100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>298200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>459200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>239600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>353300</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3622,8 +3794,14 @@
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3720,44 +3898,50 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>416100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>408800</v>
+      </c>
+      <c r="F43" s="3">
         <v>1016900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1058200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1335000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1121900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1134000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1292300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1198600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1134000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1292300</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
@@ -3818,8 +4002,14 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3850,11 +4040,11 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -3916,44 +4106,50 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>149700</v>
+      </c>
+      <c r="F45" s="3">
         <v>156800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>163200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>136300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>22000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>22400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>79100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>19000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>22400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>79100</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
@@ -4014,44 +4210,50 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1118400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1098800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1817600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1891400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2102100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1713000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1785400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1895800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1553500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1785400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1895800</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
@@ -4112,95 +4314,101 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E47" s="3">
         <v>38400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
+        <v>38400</v>
+      </c>
+      <c r="G47" s="3">
         <v>39900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>63800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>81900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>71900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>82300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>135300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>71900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>82300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1393000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1434400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>10415800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1662800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1704000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1472900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1331000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1325400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1416600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1627500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1700800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1754300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>2077200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>2235500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>2303200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>2469600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>2500700</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4210,95 +4418,101 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>26600</v>
+      </c>
+      <c r="F48" s="3">
         <v>29100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>30300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>4600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>4700</v>
       </c>
       <c r="I48" s="3">
         <v>4600</v>
       </c>
       <c r="J48" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="L48" s="3">
         <v>2600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>19200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>3900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>4700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>7300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>8300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>10800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>15200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>3200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>3300</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4308,16 +4522,22 @@
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>400</v>
@@ -4326,10 +4546,10 @@
         <v>400</v>
       </c>
       <c r="H49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J49" s="3">
         <v>500</v>
@@ -4347,31 +4567,31 @@
         <v>500</v>
       </c>
       <c r="O49" s="3">
+        <v>500</v>
+      </c>
+      <c r="P49" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q49" s="3">
         <v>4000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>500</v>
-      </c>
-      <c r="V49" s="3">
-        <v>600</v>
-      </c>
-      <c r="W49" s="3">
-        <v>600</v>
       </c>
       <c r="X49" s="3">
         <v>600</v>
@@ -4386,17 +4606,17 @@
         <v>600</v>
       </c>
       <c r="AB49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD49" s="3">
         <v>500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>500</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4406,8 +4626,14 @@
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4730,14 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,95 +4834,101 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>235200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>231100</v>
+      </c>
+      <c r="F52" s="3">
         <v>155300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>161600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>123400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>275100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>224500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>105300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>265800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>224500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>105300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>21100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>13400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>12100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>10600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>40500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>43000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>39300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>31600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>26300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>23900</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4700,8 +4938,14 @@
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,95 +5042,101 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1465300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1439600</v>
+      </c>
+      <c r="F54" s="3">
         <v>2058800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2142300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2307800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2089100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2101200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2099700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1961000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2101200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2099700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1813500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1881100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>14386200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2057100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2049700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1902000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1702900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1657700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1776800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1946900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2005800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2052200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2439100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2603200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2810900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2756600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2901400</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4896,8 +5146,14 @@
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5188,10 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,8 +5226,10 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5000,11 +5260,11 @@
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -5066,89 +5326,95 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>460500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>452400</v>
+      </c>
+      <c r="F58" s="3">
         <v>962300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1001400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1005200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>69800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>46400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>839200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>46400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>839200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>2600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>45300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>41400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>47900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>51000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>70800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>105600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>143200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>85000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>134100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>214700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>340900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>496400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>612000</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
@@ -5164,95 +5430,101 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>37900</v>
+      </c>
+      <c r="F59" s="3">
         <v>28700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>29800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>26000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>28800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>30500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>28500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>23900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>30500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>28500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>27400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>24300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>194700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>31400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>27600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>28900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>28400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>51800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>45300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>27300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>32700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>124900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>126800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>124100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>106200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>92400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>88200</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5262,44 +5534,50 @@
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>501700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>492900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1001600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1042200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1045300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>101700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>79100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>885600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>28000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>79100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>885600</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
       <c r="O60" s="3">
         <v>0</v>
       </c>
@@ -5360,95 +5638,101 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>32400</v>
+      </c>
+      <c r="F61" s="3">
         <v>82200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>85500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>257900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>986200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1052800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>301700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1069600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1052800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>301700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>965500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1033100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8041900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1150300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1091200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>961200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>786400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>738400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>804400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1007400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1024300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1014700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1334100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1429700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1613600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1710400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1789000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5458,79 +5742,85 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>398600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>391600</v>
+      </c>
+      <c r="F62" s="3">
         <v>404900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>421300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>423400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>422200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>372700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>325700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>308400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>372700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>325700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>9700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>15100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>151800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>29100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>52000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>55700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>55200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>23200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>30900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>53200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>55300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>100</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>200</v>
       </c>
       <c r="AA62" s="3">
         <v>200</v>
@@ -5539,14 +5829,14 @@
         <v>200</v>
       </c>
       <c r="AC62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE62" s="3">
         <v>100</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5556,8 +5846,14 @@
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5950,14 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +6054,14 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,95 +6158,101 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>953400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>936700</v>
+      </c>
+      <c r="F66" s="3">
         <v>1502900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1563800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1742400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1519600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1515300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1528800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1415600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1515300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1528800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1280900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1344700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10567900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1516500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1495500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1351300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1182100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1152000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1249900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1389200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1451700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1507400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1916400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2119700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2368600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2401800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2572900</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5948,8 +6262,14 @@
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6304,10 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6404,14 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6508,14 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6278,8 +6612,14 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,95 +6716,101 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>381900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>375200</v>
+      </c>
+      <c r="F72" s="3">
         <v>430400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>447900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>437700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>423100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>437500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>429000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>412100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>437500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>429000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>398700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>398600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2824300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>403600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>413600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>408600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>384100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>369400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>383700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>406800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>409900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>400500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>378100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>344300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>309000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>271400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>244600</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6474,8 +6820,14 @@
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6924,14 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +7028,14 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,95 +7132,101 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>511900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>503000</v>
+      </c>
+      <c r="F76" s="3">
         <v>555900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>578500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>565400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>548700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>571200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>563400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>545400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>571200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>563400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>532700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>536400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3818300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>540600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>554200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>550700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>520800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>505700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>526900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>557700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>554100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>544800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>522700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>483500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>442300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>354800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>328500</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6866,8 +7236,14 @@
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,209 +7340,227 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>7200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>6500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>7200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-104600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>9300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>12300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>14700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>7000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-10400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>9400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>27300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>25100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>20600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>27300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>32900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>34600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>28200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>26100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>17000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>19400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,8 +7595,10 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7233,11 +7629,11 @@
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -7299,8 +7695,14 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7799,14 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7903,14 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +8007,14 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +8111,14 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,8 +8215,14 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7821,11 +8253,11 @@
       <c r="L89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
@@ -7887,8 +8319,14 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,8 +8361,10 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7955,11 +8395,11 @@
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -8021,8 +8461,14 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8565,14 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,8 +8669,14 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8249,11 +8707,11 @@
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -8315,8 +8773,14 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,8 +8815,10 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8383,11 +8849,11 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -8449,8 +8915,14 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +9019,14 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +9123,14 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,8 +9227,14 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8775,11 +9265,11 @@
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -8841,8 +9331,14 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8873,11 +9369,11 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -8939,8 +9435,14 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8971,11 +9473,11 @@
       <c r="L102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -9035,6 +9537,12 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>
